--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_construction_supplies.xlsx
@@ -1127,43 +1127,43 @@
         <v>8.9041095890411</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>337.695083852287</v>
       </c>
       <c r="G2">
         <v>1.81900452488688</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0519457013574661</v>
       </c>
       <c r="I2">
         <v>0.350174216027875</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>74.59999999999999</v>
       </c>
       <c r="L2">
-        <v>121.204981308155</v>
+        <v>120.008414125323</v>
       </c>
       <c r="M2">
         <v>108.9</v>
       </c>
       <c r="N2">
-        <v>115.304981308155</v>
+        <v>115.256414125323</v>
       </c>
       <c r="O2">
         <v>40.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.148</v>
       </c>
       <c r="Q2">
         <v>0.08878793717262889</v>
       </c>
       <c r="R2">
-        <v>0.0825069964946335</v>
+        <v>0.0825519964946335</v>
       </c>
       <c r="S2">
         <v>0.06373661666253411</v>
@@ -1185,13 +1185,13 @@
         <v>0.102287442326862</v>
       </c>
       <c r="X2">
-        <v>0.0825069964946335</v>
+        <v>0.0828777742370035</v>
       </c>
       <c r="Y2">
         <v>1.10104539097166</v>
       </c>
       <c r="Z2">
-        <v>0.715487684377053</v>
+        <v>0.722714832704094</v>
       </c>
       <c r="AA2">
         <v>40.2</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08250699649463347</v>
+        <v>0.08255199649463349</v>
       </c>
       <c r="C2">
-        <v>121.2049813081549</v>
+        <v>120.0084141253232</v>
       </c>
       <c r="D2">
-        <v>115.3049813081549</v>
+        <v>115.2564141253232</v>
       </c>
       <c r="E2">
-        <v>-40.2</v>
+        <v>-39.052</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.148</v>
       </c>
       <c r="G2">
         <v>5.9</v>
@@ -1445,28 +1445,28 @@
         <v>19.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05774439999999999</v>
       </c>
       <c r="N2">
-        <v>19.5</v>
+        <v>19.4422556</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>19.5</v>
+        <v>19.4422556</v>
       </c>
       <c r="Q2">
-        <v>22.1</v>
+        <v>22.0422556</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08250699649463347</v>
+        <v>0.08287777423700352</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7227148327040939</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>337.695083852287</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08255199649463349</v>
+        <v>0.08259699649463345</v>
       </c>
       <c r="C3">
-        <v>120.0084141253232</v>
+        <v>118.811887838871</v>
       </c>
       <c r="D3">
-        <v>115.2564141253232</v>
+        <v>115.207887838871</v>
       </c>
       <c r="E3">
-        <v>-39.052</v>
+        <v>-37.904</v>
       </c>
       <c r="F3">
-        <v>1.148</v>
+        <v>2.296</v>
       </c>
       <c r="G3">
         <v>5.9</v>
@@ -1527,28 +1527,28 @@
         <v>19.5</v>
       </c>
       <c r="M3">
-        <v>0.05774439999999999</v>
+        <v>0.1154888</v>
       </c>
       <c r="N3">
-        <v>19.4422556</v>
+        <v>19.3845112</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>19.4422556</v>
+        <v>19.3845112</v>
       </c>
       <c r="Q3">
-        <v>22.0422556</v>
+        <v>21.9845112</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08287777423700352</v>
+        <v>0.08325611887207496</v>
       </c>
       <c r="T3">
-        <v>0.7227148327040939</v>
+        <v>0.7300894738541356</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>337.695083852287</v>
+        <v>168.8475419261435</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08259699649463345</v>
+        <v>0.08264199649463345</v>
       </c>
       <c r="C4">
-        <v>118.811887838871</v>
+        <v>117.6154023971643</v>
       </c>
       <c r="D4">
-        <v>115.207887838871</v>
+        <v>115.1594023971643</v>
       </c>
       <c r="E4">
-        <v>-37.904</v>
+        <v>-36.756</v>
       </c>
       <c r="F4">
-        <v>2.296</v>
+        <v>3.444</v>
       </c>
       <c r="G4">
         <v>5.9</v>
@@ -1609,28 +1609,28 @@
         <v>19.5</v>
       </c>
       <c r="M4">
-        <v>0.1154888</v>
+        <v>0.1732332</v>
       </c>
       <c r="N4">
-        <v>19.3845112</v>
+        <v>19.3267668</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>19.3845112</v>
+        <v>19.3267668</v>
       </c>
       <c r="Q4">
-        <v>21.9845112</v>
+        <v>21.9267668</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08325611887207496</v>
+        <v>0.08364226442745717</v>
       </c>
       <c r="T4">
-        <v>0.7300894738541356</v>
+        <v>0.7376161694608792</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>168.8475419261435</v>
+        <v>112.5650279507623</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08264199649463345</v>
+        <v>0.08268699649463347</v>
       </c>
       <c r="C5">
-        <v>117.6154023971643</v>
+        <v>116.4189577486561</v>
       </c>
       <c r="D5">
-        <v>115.1594023971643</v>
+        <v>115.1109577486561</v>
       </c>
       <c r="E5">
-        <v>-36.756</v>
+        <v>-35.608</v>
       </c>
       <c r="F5">
-        <v>3.444</v>
+        <v>4.592</v>
       </c>
       <c r="G5">
         <v>5.9</v>
@@ -1691,28 +1691,28 @@
         <v>19.5</v>
       </c>
       <c r="M5">
-        <v>0.1732332</v>
+        <v>0.2309776</v>
       </c>
       <c r="N5">
-        <v>19.3267668</v>
+        <v>19.2690224</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>19.3267668</v>
+        <v>19.2690224</v>
       </c>
       <c r="Q5">
-        <v>21.9267668</v>
+        <v>21.8690224</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08364226442745717</v>
+        <v>0.08403645468190987</v>
       </c>
       <c r="T5">
-        <v>0.7376161694608792</v>
+        <v>0.7452996712260969</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>112.5650279507623</v>
+        <v>84.42377096307176</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08268699649463347</v>
+        <v>0.08273199649463346</v>
       </c>
       <c r="C6">
-        <v>116.4189577486561</v>
+        <v>115.2225538418862</v>
       </c>
       <c r="D6">
-        <v>115.1109577486561</v>
+        <v>115.0625538418862</v>
       </c>
       <c r="E6">
-        <v>-35.608</v>
+        <v>-34.46</v>
       </c>
       <c r="F6">
-        <v>4.592</v>
+        <v>5.74</v>
       </c>
       <c r="G6">
         <v>5.9</v>
@@ -1773,28 +1773,28 @@
         <v>19.5</v>
       </c>
       <c r="M6">
-        <v>0.2309776</v>
+        <v>0.288722</v>
       </c>
       <c r="N6">
-        <v>19.2690224</v>
+        <v>19.211278</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>19.2690224</v>
+        <v>19.211278</v>
       </c>
       <c r="Q6">
-        <v>21.8690224</v>
+        <v>21.811278</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08403645468190987</v>
+        <v>0.08443894367856154</v>
       </c>
       <c r="T6">
-        <v>0.7452996712260969</v>
+        <v>0.7531449309232136</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>84.42377096307176</v>
+        <v>67.53901677045739</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08273199649463346</v>
+        <v>0.08277699649463348</v>
       </c>
       <c r="C7">
-        <v>115.2225538418862</v>
+        <v>114.0261906254805</v>
       </c>
       <c r="D7">
-        <v>115.0625538418862</v>
+        <v>115.0141906254805</v>
       </c>
       <c r="E7">
-        <v>-34.46</v>
+        <v>-33.312</v>
       </c>
       <c r="F7">
-        <v>5.74</v>
+        <v>6.888000000000001</v>
       </c>
       <c r="G7">
         <v>5.9</v>
@@ -1855,28 +1855,28 @@
         <v>19.5</v>
       </c>
       <c r="M7">
-        <v>0.288722</v>
+        <v>0.3464664</v>
       </c>
       <c r="N7">
-        <v>19.211278</v>
+        <v>19.1535336</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>19.211278</v>
+        <v>19.1535336</v>
       </c>
       <c r="Q7">
-        <v>21.811278</v>
+        <v>21.7535336</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08443894367856154</v>
+        <v>0.08484999627088667</v>
       </c>
       <c r="T7">
-        <v>0.7531449309232136</v>
+        <v>0.761157111039418</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>67.53901677045739</v>
+        <v>56.28251397538116</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08277699649463346</v>
+        <v>0.08282199649463347</v>
       </c>
       <c r="C8">
-        <v>114.0261906254805</v>
+        <v>112.8298680481517</v>
       </c>
       <c r="D8">
-        <v>115.0141906254805</v>
+        <v>114.9658680481516</v>
       </c>
       <c r="E8">
-        <v>-33.312</v>
+        <v>-32.164</v>
       </c>
       <c r="F8">
-        <v>6.888</v>
+        <v>8.036</v>
       </c>
       <c r="G8">
         <v>5.9</v>
@@ -1937,28 +1937,28 @@
         <v>19.5</v>
       </c>
       <c r="M8">
-        <v>0.3464664</v>
+        <v>0.4042108</v>
       </c>
       <c r="N8">
-        <v>19.1535336</v>
+        <v>19.0957892</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>19.1535336</v>
+        <v>19.0957892</v>
       </c>
       <c r="Q8">
-        <v>21.7535336</v>
+        <v>21.6957892</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08484999627088667</v>
+        <v>0.08526988870390695</v>
       </c>
       <c r="T8">
-        <v>0.761157111039418</v>
+        <v>0.7693415961043579</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.28251397538117</v>
+        <v>48.242154836041</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08282199649463345</v>
+        <v>0.08286699649463347</v>
       </c>
       <c r="C9">
-        <v>112.8298680481517</v>
+        <v>111.6335860586983</v>
       </c>
       <c r="D9">
-        <v>114.9658680481517</v>
+        <v>114.9175860586983</v>
       </c>
       <c r="E9">
-        <v>-32.164</v>
+        <v>-31.01600000000001</v>
       </c>
       <c r="F9">
-        <v>8.036000000000001</v>
+        <v>9.183999999999999</v>
       </c>
       <c r="G9">
         <v>5.9</v>
@@ -2019,28 +2019,28 @@
         <v>19.5</v>
       </c>
       <c r="M9">
-        <v>0.4042108</v>
+        <v>0.4619552</v>
       </c>
       <c r="N9">
-        <v>19.0957892</v>
+        <v>19.0380448</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>19.0957892</v>
+        <v>19.0380448</v>
       </c>
       <c r="Q9">
-        <v>21.6957892</v>
+        <v>21.6380448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08526988870390695</v>
+        <v>0.08569890923329725</v>
       </c>
       <c r="T9">
-        <v>0.7693415961043579</v>
+        <v>0.7777040047576661</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.24215483604099</v>
+        <v>42.21188548153588</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08286699649463347</v>
+        <v>0.08291199649463347</v>
       </c>
       <c r="C10">
-        <v>111.6335860586983</v>
+        <v>110.4373446060051</v>
       </c>
       <c r="D10">
-        <v>114.9175860586983</v>
+        <v>114.8693446060051</v>
       </c>
       <c r="E10">
-        <v>-31.01600000000001</v>
+        <v>-29.868</v>
       </c>
       <c r="F10">
-        <v>9.183999999999999</v>
+        <v>10.332</v>
       </c>
       <c r="G10">
         <v>5.9</v>
@@ -2101,28 +2101,28 @@
         <v>19.5</v>
       </c>
       <c r="M10">
-        <v>0.4619552</v>
+        <v>0.5196995999999999</v>
       </c>
       <c r="N10">
-        <v>19.0380448</v>
+        <v>18.9803004</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>19.0380448</v>
+        <v>18.9803004</v>
       </c>
       <c r="Q10">
-        <v>21.6380448</v>
+        <v>21.5803004</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08569890923329725</v>
+        <v>0.08613735878531151</v>
       </c>
       <c r="T10">
-        <v>0.7777040047576661</v>
+        <v>0.7862502026121461</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.21188548153588</v>
+        <v>37.52167598358745</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08291199649463347</v>
+        <v>0.08295699649463348</v>
       </c>
       <c r="C11">
-        <v>110.4373446060051</v>
+        <v>109.2411436390424</v>
       </c>
       <c r="D11">
-        <v>114.8693446060051</v>
+        <v>114.8211436390424</v>
       </c>
       <c r="E11">
-        <v>-29.868</v>
+        <v>-28.72000000000001</v>
       </c>
       <c r="F11">
-        <v>10.332</v>
+        <v>11.48</v>
       </c>
       <c r="G11">
         <v>5.9</v>
@@ -2183,28 +2183,28 @@
         <v>19.5</v>
       </c>
       <c r="M11">
-        <v>0.5196995999999999</v>
+        <v>0.577444</v>
       </c>
       <c r="N11">
-        <v>18.9803004</v>
+        <v>18.922556</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>18.9803004</v>
+        <v>18.922556</v>
       </c>
       <c r="Q11">
-        <v>21.5803004</v>
+        <v>21.522556</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08613735878531151</v>
+        <v>0.08658555166070386</v>
       </c>
       <c r="T11">
-        <v>0.7862502026121461</v>
+        <v>0.7949863159745033</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.52167598358745</v>
+        <v>33.7695083852287</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08295699649463348</v>
+        <v>0.08300199649463347</v>
       </c>
       <c r="C12">
-        <v>109.2411436390424</v>
+        <v>108.0449831068663</v>
       </c>
       <c r="D12">
-        <v>114.8211436390424</v>
+        <v>114.7729831068663</v>
       </c>
       <c r="E12">
-        <v>-28.72</v>
+        <v>-27.572</v>
       </c>
       <c r="F12">
-        <v>11.48</v>
+        <v>12.628</v>
       </c>
       <c r="G12">
         <v>5.9</v>
@@ -2265,28 +2265,28 @@
         <v>19.5</v>
       </c>
       <c r="M12">
-        <v>0.577444</v>
+        <v>0.6351884</v>
       </c>
       <c r="N12">
-        <v>18.922556</v>
+        <v>18.8648116</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>18.922556</v>
+        <v>18.8648116</v>
       </c>
       <c r="Q12">
-        <v>21.522556</v>
+        <v>21.4648116</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08658555166070386</v>
+        <v>0.08704381628610502</v>
       </c>
       <c r="T12">
-        <v>0.7949863159745033</v>
+        <v>0.8039187464910708</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.7695083852287</v>
+        <v>30.69955307748063</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08300199649463347</v>
+        <v>0.08304699649463347</v>
       </c>
       <c r="C13">
-        <v>108.0449831068663</v>
+        <v>106.8488629586184</v>
       </c>
       <c r="D13">
-        <v>114.7729831068663</v>
+        <v>114.7248629586183</v>
       </c>
       <c r="E13">
-        <v>-27.572</v>
+        <v>-26.424</v>
       </c>
       <c r="F13">
-        <v>12.628</v>
+        <v>13.776</v>
       </c>
       <c r="G13">
         <v>5.9</v>
@@ -2347,28 +2347,28 @@
         <v>19.5</v>
       </c>
       <c r="M13">
-        <v>0.6351884</v>
+        <v>0.6929327999999999</v>
       </c>
       <c r="N13">
-        <v>18.8648116</v>
+        <v>18.8070672</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>18.8648116</v>
+        <v>18.8070672</v>
       </c>
       <c r="Q13">
-        <v>21.4648116</v>
+        <v>21.4070672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08704381628610502</v>
+        <v>0.08751249601662894</v>
       </c>
       <c r="T13">
-        <v>0.8039187464910708</v>
+        <v>0.8130541867921055</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.69955307748063</v>
+        <v>28.14125698769058</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08304699649463347</v>
+        <v>0.08309199649463347</v>
       </c>
       <c r="C14">
-        <v>106.8488629586184</v>
+        <v>105.6527831435252</v>
       </c>
       <c r="D14">
-        <v>114.7248629586183</v>
+        <v>114.6767831435252</v>
       </c>
       <c r="E14">
-        <v>-26.424</v>
+        <v>-25.276</v>
       </c>
       <c r="F14">
-        <v>13.776</v>
+        <v>14.924</v>
       </c>
       <c r="G14">
         <v>5.9</v>
@@ -2429,28 +2429,28 @@
         <v>19.5</v>
       </c>
       <c r="M14">
-        <v>0.6929327999999999</v>
+        <v>0.7506771999999999</v>
       </c>
       <c r="N14">
-        <v>18.8070672</v>
+        <v>18.7493228</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>18.8070672</v>
+        <v>18.7493228</v>
       </c>
       <c r="Q14">
-        <v>21.4070672</v>
+        <v>21.3493228</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08751249601662894</v>
+        <v>0.08799194999383157</v>
       </c>
       <c r="T14">
-        <v>0.8130541867921055</v>
+        <v>0.8223996372150033</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.14125698769058</v>
+        <v>25.97654491171439</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08309199649463347</v>
+        <v>0.08313699649463348</v>
       </c>
       <c r="C15">
-        <v>105.6527831435252</v>
+        <v>104.4567436108987</v>
       </c>
       <c r="D15">
-        <v>114.6767831435252</v>
+        <v>114.6287436108987</v>
       </c>
       <c r="E15">
-        <v>-25.276</v>
+        <v>-24.128</v>
       </c>
       <c r="F15">
-        <v>14.924</v>
+        <v>16.072</v>
       </c>
       <c r="G15">
         <v>5.9</v>
@@ -2511,28 +2511,28 @@
         <v>19.5</v>
       </c>
       <c r="M15">
-        <v>0.7506771999999999</v>
+        <v>0.8084216000000001</v>
       </c>
       <c r="N15">
-        <v>18.7493228</v>
+        <v>18.6915784</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>18.7493228</v>
+        <v>18.6915784</v>
       </c>
       <c r="Q15">
-        <v>21.3493228</v>
+        <v>21.2915784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08799194999383157</v>
+        <v>0.08848255406352729</v>
       </c>
       <c r="T15">
-        <v>0.8223996372150033</v>
+        <v>0.8319624236942476</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.97654491171439</v>
+        <v>24.1210774180205</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08313699649463348</v>
+        <v>0.08318199649463347</v>
       </c>
       <c r="C16">
-        <v>104.4567436108987</v>
+        <v>103.2607443101356</v>
       </c>
       <c r="D16">
-        <v>114.6287436108987</v>
+        <v>114.5807443101356</v>
       </c>
       <c r="E16">
-        <v>-24.128</v>
+        <v>-22.98</v>
       </c>
       <c r="F16">
-        <v>16.072</v>
+        <v>17.22</v>
       </c>
       <c r="G16">
         <v>5.9</v>
@@ -2593,28 +2593,28 @@
         <v>19.5</v>
       </c>
       <c r="M16">
-        <v>0.8084216000000001</v>
+        <v>0.8661660000000001</v>
       </c>
       <c r="N16">
-        <v>18.6915784</v>
+        <v>18.633834</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>18.6915784</v>
+        <v>18.633834</v>
       </c>
       <c r="Q16">
-        <v>21.2915784</v>
+        <v>21.233834</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08848255406352729</v>
+        <v>0.08898470175839232</v>
       </c>
       <c r="T16">
-        <v>0.8319624236942476</v>
+        <v>0.8417502169141799</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.1210774180205</v>
+        <v>22.51300559015246</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08318199649463347</v>
+        <v>0.08322699649463347</v>
       </c>
       <c r="C17">
-        <v>103.2607443101356</v>
+        <v>102.0647851907172</v>
       </c>
       <c r="D17">
-        <v>114.5807443101356</v>
+        <v>114.5327851907172</v>
       </c>
       <c r="E17">
-        <v>-22.98</v>
+        <v>-21.832</v>
       </c>
       <c r="F17">
-        <v>17.22</v>
+        <v>18.368</v>
       </c>
       <c r="G17">
         <v>5.9</v>
@@ -2675,28 +2675,28 @@
         <v>19.5</v>
       </c>
       <c r="M17">
-        <v>0.8661659999999999</v>
+        <v>0.9239103999999999</v>
       </c>
       <c r="N17">
-        <v>18.633834</v>
+        <v>18.5760896</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>18.633834</v>
+        <v>18.5760896</v>
       </c>
       <c r="Q17">
-        <v>21.233834</v>
+        <v>21.1760896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08898470175839232</v>
+        <v>0.08949880535075413</v>
       </c>
       <c r="T17">
-        <v>0.8417502169141799</v>
+        <v>0.8517710528298249</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.51300559015247</v>
+        <v>21.10594274076794</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08322699649463347</v>
+        <v>0.08327199649463347</v>
       </c>
       <c r="C18">
-        <v>102.0647851907172</v>
+        <v>100.8688662022096</v>
       </c>
       <c r="D18">
-        <v>114.5327851907172</v>
+        <v>114.4848662022096</v>
       </c>
       <c r="E18">
-        <v>-21.832</v>
+        <v>-20.684</v>
       </c>
       <c r="F18">
-        <v>18.368</v>
+        <v>19.516</v>
       </c>
       <c r="G18">
         <v>5.9</v>
@@ -2757,28 +2757,28 @@
         <v>19.5</v>
       </c>
       <c r="M18">
-        <v>0.9239103999999999</v>
+        <v>0.9816548</v>
       </c>
       <c r="N18">
-        <v>18.5760896</v>
+        <v>18.5183452</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>18.5760896</v>
+        <v>18.5183452</v>
       </c>
       <c r="Q18">
-        <v>21.1760896</v>
+        <v>21.1183452</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08949880535075413</v>
+        <v>0.09002529698148612</v>
       </c>
       <c r="T18">
-        <v>0.8517710528298249</v>
+        <v>0.8620333546711482</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.10594274076794</v>
+        <v>19.86441669719335</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08327199649463347</v>
+        <v>0.08331699649463348</v>
       </c>
       <c r="C19">
-        <v>100.8688662022096</v>
+        <v>99.67298729426319</v>
       </c>
       <c r="D19">
-        <v>114.4848662022096</v>
+        <v>114.4369872942632</v>
       </c>
       <c r="E19">
-        <v>-20.684</v>
+        <v>-19.536</v>
       </c>
       <c r="F19">
-        <v>19.516</v>
+        <v>20.664</v>
       </c>
       <c r="G19">
         <v>5.9</v>
@@ -2839,28 +2839,28 @@
         <v>19.5</v>
       </c>
       <c r="M19">
-        <v>0.9816548</v>
+        <v>1.0393992</v>
       </c>
       <c r="N19">
-        <v>18.5183452</v>
+        <v>18.4606008</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>18.5183452</v>
+        <v>18.4606008</v>
       </c>
       <c r="Q19">
-        <v>21.1183452</v>
+        <v>21.0606008</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09002529698148612</v>
+        <v>0.09056462987150424</v>
       </c>
       <c r="T19">
-        <v>0.8620333546711482</v>
+        <v>0.8725459565573815</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.86441669719335</v>
+        <v>18.76083799179372</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08331699649463348</v>
+        <v>0.08336199649463347</v>
       </c>
       <c r="C20">
-        <v>99.67298729426319</v>
+        <v>98.47714841661247</v>
       </c>
       <c r="D20">
-        <v>114.4369872942632</v>
+        <v>114.3891484166125</v>
       </c>
       <c r="E20">
-        <v>-19.536</v>
+        <v>-18.388</v>
       </c>
       <c r="F20">
-        <v>20.664</v>
+        <v>21.812</v>
       </c>
       <c r="G20">
         <v>5.9</v>
@@ -2921,28 +2921,28 @@
         <v>19.5</v>
       </c>
       <c r="M20">
-        <v>1.0393992</v>
+        <v>1.0971436</v>
       </c>
       <c r="N20">
-        <v>18.4606008</v>
+        <v>18.4028564</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>18.4606008</v>
+        <v>18.4028564</v>
       </c>
       <c r="Q20">
-        <v>21.0606008</v>
+        <v>21.0028564</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09056462987150424</v>
+        <v>0.09111727962300428</v>
       </c>
       <c r="T20">
-        <v>0.8725459565573815</v>
+        <v>0.883318128860559</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.76083799179372</v>
+        <v>17.77342546590984</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08336199649463347</v>
+        <v>0.08340699649463348</v>
       </c>
       <c r="C21">
-        <v>98.47714841661247</v>
+        <v>97.28134951907597</v>
       </c>
       <c r="D21">
-        <v>114.3891484166125</v>
+        <v>114.341349519076</v>
       </c>
       <c r="E21">
-        <v>-18.388</v>
+        <v>-17.24</v>
       </c>
       <c r="F21">
-        <v>21.812</v>
+        <v>22.96</v>
       </c>
       <c r="G21">
         <v>5.9</v>
@@ -3003,28 +3003,28 @@
         <v>19.5</v>
       </c>
       <c r="M21">
-        <v>1.0971436</v>
+        <v>1.154888</v>
       </c>
       <c r="N21">
-        <v>18.4028564</v>
+        <v>18.345112</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>18.4028564</v>
+        <v>18.345112</v>
       </c>
       <c r="Q21">
-        <v>21.0028564</v>
+        <v>20.945112</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09111727962300428</v>
+        <v>0.09168374561829185</v>
       </c>
       <c r="T21">
-        <v>0.883318128860559</v>
+        <v>0.8943596054713161</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.77342546590984</v>
+        <v>16.88475419261435</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08340699649463348</v>
+        <v>0.08345199649463347</v>
       </c>
       <c r="C22">
-        <v>97.28134951907597</v>
+        <v>96.08559055155612</v>
       </c>
       <c r="D22">
-        <v>114.341349519076</v>
+        <v>114.2935905515561</v>
       </c>
       <c r="E22">
-        <v>-17.24</v>
+        <v>-16.092</v>
       </c>
       <c r="F22">
-        <v>22.96</v>
+        <v>24.108</v>
       </c>
       <c r="G22">
         <v>5.9</v>
@@ -3085,28 +3085,28 @@
         <v>19.5</v>
       </c>
       <c r="M22">
-        <v>1.154888</v>
+        <v>1.2126324</v>
       </c>
       <c r="N22">
-        <v>18.345112</v>
+        <v>18.2873676</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>18.345112</v>
+        <v>18.2873676</v>
       </c>
       <c r="Q22">
-        <v>20.945112</v>
+        <v>20.8873676</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09168374561829185</v>
+        <v>0.09226455252485249</v>
       </c>
       <c r="T22">
-        <v>0.8943596054713161</v>
+        <v>0.9056806131355101</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.88475419261435</v>
+        <v>16.08071827868033</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08345199649463347</v>
+        <v>0.08349699649463346</v>
       </c>
       <c r="C23">
-        <v>96.08559055155612</v>
+        <v>94.88987146403902</v>
       </c>
       <c r="D23">
-        <v>114.2935905515561</v>
+        <v>114.245871464039</v>
       </c>
       <c r="E23">
-        <v>-16.09200000000001</v>
+        <v>-14.944</v>
       </c>
       <c r="F23">
-        <v>24.108</v>
+        <v>25.256</v>
       </c>
       <c r="G23">
         <v>5.9</v>
@@ -3167,28 +3167,28 @@
         <v>19.5</v>
       </c>
       <c r="M23">
-        <v>1.2126324</v>
+        <v>1.2703768</v>
       </c>
       <c r="N23">
-        <v>18.2873676</v>
+        <v>18.2296232</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>18.2873676</v>
+        <v>18.2296232</v>
       </c>
       <c r="Q23">
-        <v>20.8873676</v>
+        <v>20.8296232</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09226455252485249</v>
+        <v>0.09286025191619675</v>
       </c>
       <c r="T23">
-        <v>0.9056806131355101</v>
+        <v>0.9172919030475036</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.08071827868034</v>
+        <v>15.34977653874032</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08349699649463346</v>
+        <v>0.08354199649463347</v>
       </c>
       <c r="C24">
-        <v>94.88987146403902</v>
+        <v>93.69419220659415</v>
       </c>
       <c r="D24">
-        <v>114.245871464039</v>
+        <v>114.1981922065941</v>
       </c>
       <c r="E24">
-        <v>-14.944</v>
+        <v>-13.796</v>
       </c>
       <c r="F24">
-        <v>25.256</v>
+        <v>26.404</v>
       </c>
       <c r="G24">
         <v>5.9</v>
@@ -3249,28 +3249,28 @@
         <v>19.5</v>
       </c>
       <c r="M24">
-        <v>1.2703768</v>
+        <v>1.3281212</v>
       </c>
       <c r="N24">
-        <v>18.2296232</v>
+        <v>18.1718788</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>18.2296232</v>
+        <v>18.1718788</v>
       </c>
       <c r="Q24">
-        <v>20.8296232</v>
+        <v>20.7718788</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09286025191619675</v>
+        <v>0.0934714240190045</v>
       </c>
       <c r="T24">
-        <v>0.9172919030475036</v>
+        <v>0.9292047849052635</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.34977653874032</v>
+        <v>14.68239495009943</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08354199649463347</v>
+        <v>0.08358699649463347</v>
       </c>
       <c r="C25">
-        <v>93.69419220659415</v>
+        <v>92.49855272937444</v>
       </c>
       <c r="D25">
-        <v>114.1981922065941</v>
+        <v>114.1505527293744</v>
       </c>
       <c r="E25">
-        <v>-13.796</v>
+        <v>-12.648</v>
       </c>
       <c r="F25">
-        <v>26.404</v>
+        <v>27.552</v>
       </c>
       <c r="G25">
         <v>5.9</v>
@@ -3331,28 +3331,28 @@
         <v>19.5</v>
       </c>
       <c r="M25">
-        <v>1.3281212</v>
+        <v>1.3858656</v>
       </c>
       <c r="N25">
-        <v>18.1718788</v>
+        <v>18.1141344</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>18.1718788</v>
+        <v>18.1141344</v>
       </c>
       <c r="Q25">
-        <v>20.7718788</v>
+        <v>20.7141344</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0934714240190045</v>
+        <v>0.09409867959820194</v>
       </c>
       <c r="T25">
-        <v>0.9292047849052635</v>
+        <v>0.941431163654017</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.68239495009943</v>
+        <v>14.07062849384529</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08358699649463347</v>
+        <v>0.08363199649463346</v>
       </c>
       <c r="C26">
-        <v>92.49855272937444</v>
+        <v>91.30295298261592</v>
       </c>
       <c r="D26">
-        <v>114.1505527293744</v>
+        <v>114.1029529826159</v>
       </c>
       <c r="E26">
-        <v>-12.648</v>
+        <v>-11.5</v>
       </c>
       <c r="F26">
-        <v>27.552</v>
+        <v>28.7</v>
       </c>
       <c r="G26">
         <v>5.9</v>
@@ -3413,28 +3413,28 @@
         <v>19.5</v>
       </c>
       <c r="M26">
-        <v>1.3858656</v>
+        <v>1.44361</v>
       </c>
       <c r="N26">
-        <v>18.1141344</v>
+        <v>18.05639</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>18.1141344</v>
+        <v>18.05639</v>
       </c>
       <c r="Q26">
-        <v>20.7141344</v>
+        <v>20.65639</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09409867959820194</v>
+        <v>0.09474266199284462</v>
       </c>
       <c r="T26">
-        <v>0.941431163654017</v>
+        <v>0.9539835791694038</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.07062849384529</v>
+        <v>13.50780335409148</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08363199649463346</v>
+        <v>0.08367699649463345</v>
       </c>
       <c r="C27">
-        <v>91.30295298261592</v>
+        <v>90.10739291663756</v>
       </c>
       <c r="D27">
-        <v>114.1029529826159</v>
+        <v>114.0553929166376</v>
       </c>
       <c r="E27">
-        <v>-11.5</v>
+        <v>-10.352</v>
       </c>
       <c r="F27">
-        <v>28.7</v>
+        <v>29.848</v>
       </c>
       <c r="G27">
         <v>5.9</v>
@@ -3495,28 +3495,28 @@
         <v>19.5</v>
       </c>
       <c r="M27">
-        <v>1.44361</v>
+        <v>1.5013544</v>
       </c>
       <c r="N27">
-        <v>18.05639</v>
+        <v>17.9986456</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>18.05639</v>
+        <v>17.9986456</v>
       </c>
       <c r="Q27">
-        <v>20.65639</v>
+        <v>20.5986456</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09474266199284462</v>
+        <v>0.09540404931707225</v>
       </c>
       <c r="T27">
-        <v>0.9539835791694038</v>
+        <v>0.9668752491581796</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.50780335409148</v>
+        <v>12.98827245585719</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08367699649463345</v>
+        <v>0.08412699649463347</v>
       </c>
       <c r="C28">
-        <v>90.10739291663756</v>
+        <v>88.48596382891884</v>
       </c>
       <c r="D28">
-        <v>114.0553929166376</v>
+        <v>113.5819638289188</v>
       </c>
       <c r="E28">
-        <v>-10.352</v>
+        <v>-9.204000000000001</v>
       </c>
       <c r="F28">
-        <v>29.848</v>
+        <v>30.996</v>
       </c>
       <c r="G28">
         <v>5.9</v>
@@ -3577,45 +3577,45 @@
         <v>19.5</v>
       </c>
       <c r="M28">
-        <v>1.5013544</v>
+        <v>1.6055928</v>
       </c>
       <c r="N28">
-        <v>17.9986456</v>
+        <v>17.8944072</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>17.9986456</v>
+        <v>17.8944072</v>
       </c>
       <c r="Q28">
-        <v>20.5986456</v>
+        <v>20.4944072</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09540404931707225</v>
+        <v>0.09608355684196367</v>
       </c>
       <c r="T28">
-        <v>0.9668752491581796</v>
+        <v>0.9801201155850041</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>12.98827245585719</v>
+        <v>12.14504698825256</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08412699649463347</v>
+        <v>0.08418699649463347</v>
       </c>
       <c r="C29">
-        <v>88.48596382891884</v>
+        <v>87.27513674116595</v>
       </c>
       <c r="D29">
-        <v>113.5819638289188</v>
+        <v>113.519136741166</v>
       </c>
       <c r="E29">
-        <v>-9.204000000000001</v>
+        <v>-8.055999999999997</v>
       </c>
       <c r="F29">
-        <v>30.996</v>
+        <v>32.14400000000001</v>
       </c>
       <c r="G29">
         <v>5.9</v>
@@ -3659,28 +3659,28 @@
         <v>19.5</v>
       </c>
       <c r="M29">
-        <v>1.6055928</v>
+        <v>1.6650592</v>
       </c>
       <c r="N29">
-        <v>17.8944072</v>
+        <v>17.8349408</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>17.8944072</v>
+        <v>17.8349408</v>
       </c>
       <c r="Q29">
-        <v>20.4944072</v>
+        <v>20.4349408</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09608355684196367</v>
+        <v>0.09678193957587983</v>
       </c>
       <c r="T29">
-        <v>0.9801201155850041</v>
+        <v>0.993732894968129</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.14504698825256</v>
+        <v>11.71129531010068</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08418699649463347</v>
+        <v>0.08424699649463348</v>
       </c>
       <c r="C30">
-        <v>87.27513674116595</v>
+        <v>86.06437911973744</v>
       </c>
       <c r="D30">
-        <v>113.519136741166</v>
+        <v>113.4563791197374</v>
       </c>
       <c r="E30">
-        <v>-8.055999999999997</v>
+        <v>-6.908000000000001</v>
       </c>
       <c r="F30">
-        <v>32.14400000000001</v>
+        <v>33.292</v>
       </c>
       <c r="G30">
         <v>5.9</v>
@@ -3741,28 +3741,28 @@
         <v>19.5</v>
       </c>
       <c r="M30">
-        <v>1.6650592</v>
+        <v>1.7245256</v>
       </c>
       <c r="N30">
-        <v>17.8349408</v>
+        <v>17.7754744</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>17.8349408</v>
+        <v>17.7754744</v>
       </c>
       <c r="Q30">
-        <v>20.4349408</v>
+        <v>20.3754744</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09678193957587983</v>
+        <v>0.09749999506286405</v>
       </c>
       <c r="T30">
-        <v>0.993732894968129</v>
+        <v>1.007729132925427</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.71129531010068</v>
+        <v>11.30745754078687</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08424699649463346</v>
+        <v>0.08430699649463345</v>
       </c>
       <c r="C31">
-        <v>86.06437911973745</v>
+        <v>84.85369084948626</v>
       </c>
       <c r="D31">
-        <v>113.4563791197374</v>
+        <v>113.3936908494862</v>
       </c>
       <c r="E31">
-        <v>-6.908000000000008</v>
+        <v>-5.760000000000005</v>
       </c>
       <c r="F31">
-        <v>33.29199999999999</v>
+        <v>34.44</v>
       </c>
       <c r="G31">
         <v>5.9</v>
@@ -3823,28 +3823,28 @@
         <v>19.5</v>
       </c>
       <c r="M31">
-        <v>1.7245256</v>
+        <v>1.783992</v>
       </c>
       <c r="N31">
-        <v>17.7754744</v>
+        <v>17.716008</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>17.7754744</v>
+        <v>17.716008</v>
       </c>
       <c r="Q31">
-        <v>20.3754744</v>
+        <v>20.316008</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09749999506286404</v>
+        <v>0.09823856642090495</v>
       </c>
       <c r="T31">
-        <v>1.007729132925427</v>
+        <v>1.02212526339579</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.30745754078687</v>
+        <v>10.93054228942731</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08430699649463345</v>
+        <v>0.08436699649463347</v>
       </c>
       <c r="C32">
-        <v>84.85369084948626</v>
+        <v>83.64307181551962</v>
       </c>
       <c r="D32">
-        <v>113.3936908494862</v>
+        <v>113.3310718155196</v>
       </c>
       <c r="E32">
-        <v>-5.760000000000005</v>
+        <v>-4.612000000000002</v>
       </c>
       <c r="F32">
-        <v>34.44</v>
+        <v>35.588</v>
       </c>
       <c r="G32">
         <v>5.9</v>
@@ -3905,28 +3905,28 @@
         <v>19.5</v>
       </c>
       <c r="M32">
-        <v>1.783992</v>
+        <v>1.8434584</v>
       </c>
       <c r="N32">
-        <v>17.716008</v>
+        <v>17.6565416</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>17.716008</v>
+        <v>17.6565416</v>
       </c>
       <c r="Q32">
-        <v>20.316008</v>
+        <v>20.2565416</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09823856642090495</v>
+        <v>0.09899854564439634</v>
       </c>
       <c r="T32">
-        <v>1.02212526339579</v>
+        <v>1.036938673010222</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.93054228942731</v>
+        <v>10.57794415105868</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08436699649463347</v>
+        <v>0.08442699649463348</v>
       </c>
       <c r="C33">
-        <v>83.64307181551962</v>
+        <v>82.43252190319848</v>
       </c>
       <c r="D33">
-        <v>113.3310718155196</v>
+        <v>113.2685219031985</v>
       </c>
       <c r="E33">
-        <v>-4.612000000000002</v>
+        <v>-3.464000000000006</v>
       </c>
       <c r="F33">
-        <v>35.588</v>
+        <v>36.736</v>
       </c>
       <c r="G33">
         <v>5.9</v>
@@ -3987,28 +3987,28 @@
         <v>19.5</v>
       </c>
       <c r="M33">
-        <v>1.8434584</v>
+        <v>1.9029248</v>
       </c>
       <c r="N33">
-        <v>17.6565416</v>
+        <v>17.5970752</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>17.6565416</v>
+        <v>17.5970752</v>
       </c>
       <c r="Q33">
-        <v>20.2565416</v>
+        <v>20.1970752</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09899854564439634</v>
+        <v>0.09978087719799041</v>
       </c>
       <c r="T33">
-        <v>1.036938673010222</v>
+        <v>1.052187771142725</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.57794415105868</v>
+        <v>10.2473833963381</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08442699649463348</v>
+        <v>0.08448699649463347</v>
       </c>
       <c r="C34">
-        <v>82.43252190319848</v>
+        <v>81.22204099813668</v>
       </c>
       <c r="D34">
-        <v>113.2685219031985</v>
+        <v>113.2060409981367</v>
       </c>
       <c r="E34">
-        <v>-3.464000000000006</v>
+        <v>-2.316000000000003</v>
       </c>
       <c r="F34">
-        <v>36.736</v>
+        <v>37.884</v>
       </c>
       <c r="G34">
         <v>5.9</v>
@@ -4069,28 +4069,28 @@
         <v>19.5</v>
       </c>
       <c r="M34">
-        <v>1.9029248</v>
+        <v>1.9623912</v>
       </c>
       <c r="N34">
-        <v>17.5970752</v>
+        <v>17.5376088</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>17.5970752</v>
+        <v>17.5376088</v>
       </c>
       <c r="Q34">
-        <v>20.1970752</v>
+        <v>20.1376088</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09978087719799041</v>
+        <v>0.1005865619322888</v>
       </c>
       <c r="T34">
-        <v>1.052187771142725</v>
+        <v>1.067892066234407</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.2473833963381</v>
+        <v>9.936856626752098</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08448699649463347</v>
+        <v>0.08512499649463345</v>
       </c>
       <c r="C35">
-        <v>81.22204099813668</v>
+        <v>79.41389927475856</v>
       </c>
       <c r="D35">
-        <v>113.2060409981367</v>
+        <v>112.5458992747586</v>
       </c>
       <c r="E35">
-        <v>-2.316000000000003</v>
+        <v>-1.167999999999999</v>
       </c>
       <c r="F35">
-        <v>37.884</v>
+        <v>39.032</v>
       </c>
       <c r="G35">
         <v>5.9</v>
@@ -4151,45 +4151,45 @@
         <v>19.5</v>
       </c>
       <c r="M35">
-        <v>1.9623912</v>
+        <v>2.088212</v>
       </c>
       <c r="N35">
-        <v>17.5376088</v>
+        <v>17.411788</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>17.5376088</v>
+        <v>17.411788</v>
       </c>
       <c r="Q35">
-        <v>20.1376088</v>
+        <v>20.011788</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1005865619322888</v>
+        <v>0.1014166613555053</v>
       </c>
       <c r="T35">
-        <v>1.067892066234407</v>
+        <v>1.084072249056141</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.936856626752098</v>
+        <v>9.338132335222669</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08512499649463345</v>
+        <v>0.08520199649463346</v>
       </c>
       <c r="C36">
-        <v>79.41389927475856</v>
+        <v>78.18674729876409</v>
       </c>
       <c r="D36">
-        <v>112.5458992747586</v>
+        <v>112.4667472987641</v>
       </c>
       <c r="E36">
-        <v>-1.167999999999999</v>
+        <v>-0.02000000000000313</v>
       </c>
       <c r="F36">
-        <v>39.032</v>
+        <v>40.18</v>
       </c>
       <c r="G36">
         <v>5.9</v>
@@ -4233,28 +4233,28 @@
         <v>19.5</v>
       </c>
       <c r="M36">
-        <v>2.088212</v>
+        <v>2.14963</v>
       </c>
       <c r="N36">
-        <v>17.411788</v>
+        <v>17.35037</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>17.411788</v>
+        <v>17.35037</v>
       </c>
       <c r="Q36">
-        <v>20.011788</v>
+        <v>19.95037</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1014166613555053</v>
+        <v>0.1022723022994361</v>
       </c>
       <c r="T36">
-        <v>1.084072249056141</v>
+        <v>1.100750283657004</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.338132335222669</v>
+        <v>9.071328554216306</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08520199649463346</v>
+        <v>0.08527899649463345</v>
       </c>
       <c r="C37">
-        <v>78.18674729876409</v>
+        <v>76.95970657750796</v>
       </c>
       <c r="D37">
-        <v>112.4667472987641</v>
+        <v>112.387706577508</v>
       </c>
       <c r="E37">
-        <v>-0.02000000000000313</v>
+        <v>1.128</v>
       </c>
       <c r="F37">
-        <v>40.18</v>
+        <v>41.328</v>
       </c>
       <c r="G37">
         <v>5.9</v>
@@ -4315,28 +4315,28 @@
         <v>19.5</v>
       </c>
       <c r="M37">
-        <v>2.14963</v>
+        <v>2.211048</v>
       </c>
       <c r="N37">
-        <v>17.35037</v>
+        <v>17.288952</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>17.35037</v>
+        <v>17.288952</v>
       </c>
       <c r="Q37">
-        <v>19.95037</v>
+        <v>19.888952</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1022723022994361</v>
+        <v>0.1031546820228648</v>
       </c>
       <c r="T37">
-        <v>1.100750283657004</v>
+        <v>1.117949506839145</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.071328554216306</v>
+        <v>8.819347205488079</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08527899649463347</v>
+        <v>0.08535599649463346</v>
       </c>
       <c r="C38">
-        <v>76.95970657750797</v>
+        <v>75.73277687658812</v>
       </c>
       <c r="D38">
-        <v>112.387706577508</v>
+        <v>112.3087768765881</v>
       </c>
       <c r="E38">
-        <v>1.127999999999993</v>
+        <v>2.275999999999996</v>
       </c>
       <c r="F38">
-        <v>41.328</v>
+        <v>42.476</v>
       </c>
       <c r="G38">
         <v>5.9</v>
@@ -4397,28 +4397,28 @@
         <v>19.5</v>
       </c>
       <c r="M38">
-        <v>2.211048</v>
+        <v>2.272466</v>
       </c>
       <c r="N38">
-        <v>17.288952</v>
+        <v>17.227534</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>17.288952</v>
+        <v>17.227534</v>
       </c>
       <c r="Q38">
-        <v>19.888952</v>
+        <v>19.827534</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1031546820228648</v>
+        <v>0.1040650738010055</v>
       </c>
       <c r="T38">
-        <v>1.117949506839145</v>
+        <v>1.135694737106433</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.819347205488079</v>
+        <v>8.580986470204614</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08535599649463346</v>
+        <v>0.08543299649463346</v>
       </c>
       <c r="C39">
-        <v>75.73277687658812</v>
+        <v>74.50595796226054</v>
       </c>
       <c r="D39">
-        <v>112.3087768765881</v>
+        <v>112.2299579622605</v>
       </c>
       <c r="E39">
-        <v>2.275999999999996</v>
+        <v>3.423999999999999</v>
       </c>
       <c r="F39">
-        <v>42.476</v>
+        <v>43.624</v>
       </c>
       <c r="G39">
         <v>5.9</v>
@@ -4479,28 +4479,28 @@
         <v>19.5</v>
       </c>
       <c r="M39">
-        <v>2.272466</v>
+        <v>2.333884</v>
       </c>
       <c r="N39">
-        <v>17.227534</v>
+        <v>17.166116</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>17.227534</v>
+        <v>17.166116</v>
       </c>
       <c r="Q39">
-        <v>19.827534</v>
+        <v>19.766116</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1040650738010055</v>
+        <v>0.1050048330558604</v>
       </c>
       <c r="T39">
-        <v>1.135694737106433</v>
+        <v>1.154012394156537</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.580986470204614</v>
+        <v>8.355171036778177</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08543299649463346</v>
+        <v>0.08550999649463348</v>
       </c>
       <c r="C40">
-        <v>74.50595796226054</v>
+        <v>73.27924960143685</v>
       </c>
       <c r="D40">
-        <v>112.2299579622605</v>
+        <v>112.1512496014368</v>
       </c>
       <c r="E40">
-        <v>3.423999999999999</v>
+        <v>4.571999999999996</v>
       </c>
       <c r="F40">
-        <v>43.624</v>
+        <v>44.772</v>
       </c>
       <c r="G40">
         <v>5.9</v>
@@ -4561,28 +4561,28 @@
         <v>19.5</v>
       </c>
       <c r="M40">
-        <v>2.333884</v>
+        <v>2.395302</v>
       </c>
       <c r="N40">
-        <v>17.166116</v>
+        <v>17.104698</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>17.166116</v>
+        <v>17.104698</v>
       </c>
       <c r="Q40">
-        <v>19.766116</v>
+        <v>19.704698</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1050048330558604</v>
+        <v>0.1059754040895631</v>
       </c>
       <c r="T40">
-        <v>1.154012394156537</v>
+        <v>1.172930630126316</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.355171036778177</v>
+        <v>8.140935881988993</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08550999649463348</v>
+        <v>0.08558699649463347</v>
       </c>
       <c r="C41">
-        <v>73.27924960143685</v>
+        <v>72.05265156168215</v>
       </c>
       <c r="D41">
-        <v>112.1512496014368</v>
+        <v>112.0726515616822</v>
       </c>
       <c r="E41">
-        <v>4.571999999999996</v>
+        <v>5.719999999999999</v>
       </c>
       <c r="F41">
-        <v>44.772</v>
+        <v>45.92</v>
       </c>
       <c r="G41">
         <v>5.9</v>
@@ -4643,28 +4643,28 @@
         <v>19.5</v>
       </c>
       <c r="M41">
-        <v>2.395302</v>
+        <v>2.45672</v>
       </c>
       <c r="N41">
-        <v>17.104698</v>
+        <v>17.04328</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>17.104698</v>
+        <v>17.04328</v>
       </c>
       <c r="Q41">
-        <v>19.704698</v>
+        <v>19.64328</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1059754040895631</v>
+        <v>0.1069783274910558</v>
       </c>
       <c r="T41">
-        <v>1.172930630126316</v>
+        <v>1.192479473961755</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.140935881988993</v>
+        <v>7.937412484939268</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08558699649463347</v>
+        <v>0.08566399649463345</v>
       </c>
       <c r="C42">
-        <v>72.05265156168215</v>
+        <v>70.82616361121273</v>
       </c>
       <c r="D42">
-        <v>112.0726515616822</v>
+        <v>111.9941636112127</v>
       </c>
       <c r="E42">
-        <v>5.719999999999999</v>
+        <v>6.868000000000002</v>
       </c>
       <c r="F42">
-        <v>45.92</v>
+        <v>47.068</v>
       </c>
       <c r="G42">
         <v>5.9</v>
@@ -4725,28 +4725,28 @@
         <v>19.5</v>
       </c>
       <c r="M42">
-        <v>2.45672</v>
+        <v>2.518138</v>
       </c>
       <c r="N42">
-        <v>17.04328</v>
+        <v>16.981862</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>17.04328</v>
+        <v>16.981862</v>
       </c>
       <c r="Q42">
-        <v>19.64328</v>
+        <v>19.581862</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1069783274910558</v>
+        <v>0.1080152482959889</v>
       </c>
       <c r="T42">
-        <v>1.192479473961755</v>
+        <v>1.212690990469581</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.937412484939268</v>
+        <v>7.743817058477334</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08566399649463345</v>
+        <v>0.08607699649463348</v>
       </c>
       <c r="C43">
-        <v>70.82616361121273</v>
+        <v>69.25905192978402</v>
       </c>
       <c r="D43">
-        <v>111.9941636112127</v>
+        <v>111.575051929784</v>
       </c>
       <c r="E43">
-        <v>6.868000000000002</v>
+        <v>8.015999999999998</v>
       </c>
       <c r="F43">
-        <v>47.068</v>
+        <v>48.216</v>
       </c>
       <c r="G43">
         <v>5.9</v>
@@ -4807,45 +4807,45 @@
         <v>19.5</v>
       </c>
       <c r="M43">
-        <v>2.518138</v>
+        <v>2.6181288</v>
       </c>
       <c r="N43">
-        <v>16.981862</v>
+        <v>16.8818712</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>16.981862</v>
+        <v>16.8818712</v>
       </c>
       <c r="Q43">
-        <v>19.581862</v>
+        <v>19.4818712</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1080152482959889</v>
+        <v>0.1090879249907474</v>
       </c>
       <c r="T43">
-        <v>1.212690990469581</v>
+        <v>1.233599455822505</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.743817058477334</v>
+        <v>7.448067490033339</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08607699649463346</v>
+        <v>0.08616199649463346</v>
       </c>
       <c r="C44">
-        <v>69.25905192978405</v>
+        <v>68.02518301349275</v>
       </c>
       <c r="D44">
-        <v>111.575051929784</v>
+        <v>111.4891830134927</v>
       </c>
       <c r="E44">
-        <v>8.015999999999991</v>
+        <v>9.163999999999994</v>
       </c>
       <c r="F44">
-        <v>48.21599999999999</v>
+        <v>49.364</v>
       </c>
       <c r="G44">
         <v>5.9</v>
@@ -4889,28 +4889,28 @@
         <v>19.5</v>
       </c>
       <c r="M44">
-        <v>2.6181288</v>
+        <v>2.6804652</v>
       </c>
       <c r="N44">
-        <v>16.8818712</v>
+        <v>16.8195348</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>16.8818712</v>
+        <v>16.8195348</v>
       </c>
       <c r="Q44">
-        <v>19.4818712</v>
+        <v>19.4195348</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1090879249907473</v>
+        <v>0.1101982394642692</v>
       </c>
       <c r="T44">
-        <v>1.233599455822505</v>
+        <v>1.255241551538689</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.44806749003334</v>
+        <v>7.274856618172099</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08616199649463346</v>
+        <v>0.08624699649463347</v>
       </c>
       <c r="C45">
-        <v>68.02518301349275</v>
+        <v>66.7914461661604</v>
       </c>
       <c r="D45">
-        <v>111.4891830134927</v>
+        <v>111.4034461661604</v>
       </c>
       <c r="E45">
-        <v>9.163999999999994</v>
+        <v>10.312</v>
       </c>
       <c r="F45">
-        <v>49.364</v>
+        <v>50.512</v>
       </c>
       <c r="G45">
         <v>5.9</v>
@@ -4971,28 +4971,28 @@
         <v>19.5</v>
       </c>
       <c r="M45">
-        <v>2.6804652</v>
+        <v>2.7428016</v>
       </c>
       <c r="N45">
-        <v>16.8195348</v>
+        <v>16.7571984</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>16.8195348</v>
+        <v>16.7571984</v>
       </c>
       <c r="Q45">
-        <v>19.4195348</v>
+        <v>19.3571984</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1101982394642692</v>
+        <v>0.1113482080261312</v>
       </c>
       <c r="T45">
-        <v>1.255241551538689</v>
+        <v>1.277656579244737</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.274856618172099</v>
+        <v>7.109518967759097</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08624699649463347</v>
+        <v>0.08633199649463347</v>
       </c>
       <c r="C46">
-        <v>66.7914461661604</v>
+        <v>65.55784108333211</v>
       </c>
       <c r="D46">
-        <v>111.4034461661604</v>
+        <v>111.3178410833321</v>
       </c>
       <c r="E46">
-        <v>10.312</v>
+        <v>11.45999999999999</v>
       </c>
       <c r="F46">
-        <v>50.512</v>
+        <v>51.66</v>
       </c>
       <c r="G46">
         <v>5.9</v>
@@ -5053,28 +5053,28 @@
         <v>19.5</v>
       </c>
       <c r="M46">
-        <v>2.7428016</v>
+        <v>2.805138</v>
       </c>
       <c r="N46">
-        <v>16.7571984</v>
+        <v>16.694862</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>16.7571984</v>
+        <v>16.694862</v>
       </c>
       <c r="Q46">
-        <v>19.3571984</v>
+        <v>19.294862</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1113482080261312</v>
+        <v>0.1125399936266063</v>
       </c>
       <c r="T46">
-        <v>1.277656579244737</v>
+        <v>1.300886698867369</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.109518967759097</v>
+        <v>6.951529657364451</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08633199649463347</v>
+        <v>0.08641699649463347</v>
       </c>
       <c r="C47">
-        <v>65.55784108333211</v>
+        <v>64.32436746148807</v>
       </c>
       <c r="D47">
-        <v>111.3178410833321</v>
+        <v>111.2323674614881</v>
       </c>
       <c r="E47">
-        <v>11.45999999999999</v>
+        <v>12.608</v>
       </c>
       <c r="F47">
-        <v>51.66</v>
+        <v>52.808</v>
       </c>
       <c r="G47">
         <v>5.9</v>
@@ -5135,28 +5135,28 @@
         <v>19.5</v>
       </c>
       <c r="M47">
-        <v>2.805138</v>
+        <v>2.8674744</v>
       </c>
       <c r="N47">
-        <v>16.694862</v>
+        <v>16.6325256</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>16.694862</v>
+        <v>16.6325256</v>
       </c>
       <c r="Q47">
-        <v>19.294862</v>
+        <v>19.2325256</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1125399936266063</v>
+        <v>0.1137759194345064</v>
       </c>
       <c r="T47">
-        <v>1.300886698867369</v>
+        <v>1.324977193290839</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.951529657364451</v>
+        <v>6.800409447421746</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08641699649463347</v>
+        <v>0.08650199649463347</v>
       </c>
       <c r="C48">
-        <v>64.32436746148807</v>
+        <v>63.09102499804</v>
       </c>
       <c r="D48">
-        <v>111.2323674614881</v>
+        <v>111.14702499804</v>
       </c>
       <c r="E48">
-        <v>12.608</v>
+        <v>13.756</v>
       </c>
       <c r="F48">
-        <v>52.808</v>
+        <v>53.956</v>
       </c>
       <c r="G48">
         <v>5.9</v>
@@ -5217,28 +5217,28 @@
         <v>19.5</v>
       </c>
       <c r="M48">
-        <v>2.8674744</v>
+        <v>2.9298108</v>
       </c>
       <c r="N48">
-        <v>16.6325256</v>
+        <v>16.5701892</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>16.6325256</v>
+        <v>16.5701892</v>
       </c>
       <c r="Q48">
-        <v>19.2325256</v>
+        <v>19.1701892</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1137759194345064</v>
+        <v>0.1150584839521386</v>
       </c>
       <c r="T48">
-        <v>1.324977193290839</v>
+        <v>1.349976762975571</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.800409447421746</v>
+        <v>6.655719884710644</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08650199649463347</v>
+        <v>0.08658699649463349</v>
       </c>
       <c r="C49">
-        <v>63.09102499804</v>
+        <v>61.8578133913275</v>
       </c>
       <c r="D49">
-        <v>111.14702499804</v>
+        <v>111.0618133913275</v>
       </c>
       <c r="E49">
-        <v>13.756</v>
+        <v>14.904</v>
       </c>
       <c r="F49">
-        <v>53.956</v>
+        <v>55.10400000000001</v>
       </c>
       <c r="G49">
         <v>5.9</v>
@@ -5299,28 +5299,28 @@
         <v>19.5</v>
       </c>
       <c r="M49">
-        <v>2.9298108</v>
+        <v>2.9921472</v>
       </c>
       <c r="N49">
-        <v>16.5701892</v>
+        <v>16.5078528</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>16.5701892</v>
+        <v>16.5078528</v>
       </c>
       <c r="Q49">
-        <v>19.1701892</v>
+        <v>19.1078528</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1150584839521386</v>
+        <v>0.1163903778742952</v>
       </c>
       <c r="T49">
-        <v>1.349976762975571</v>
+        <v>1.375937854571256</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.655719884710644</v>
+        <v>6.517059053779171</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08658699649463347</v>
+        <v>0.08667199649463347</v>
       </c>
       <c r="C50">
-        <v>61.85781339132754</v>
+        <v>60.62473234061467</v>
       </c>
       <c r="D50">
-        <v>111.0618133913275</v>
+        <v>110.9767323406147</v>
       </c>
       <c r="E50">
-        <v>14.904</v>
+        <v>16.05199999999999</v>
       </c>
       <c r="F50">
-        <v>55.104</v>
+        <v>56.252</v>
       </c>
       <c r="G50">
         <v>5.9</v>
@@ -5381,28 +5381,28 @@
         <v>19.5</v>
       </c>
       <c r="M50">
-        <v>2.9921472</v>
+        <v>3.0544836</v>
       </c>
       <c r="N50">
-        <v>16.5078528</v>
+        <v>16.4455164</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>16.5078528</v>
+        <v>16.4455164</v>
       </c>
       <c r="Q50">
-        <v>19.1078528</v>
+        <v>19.0455164</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1163903778742951</v>
+        <v>0.1177745029306539</v>
       </c>
       <c r="T50">
-        <v>1.375937854571256</v>
+        <v>1.4029170281903</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.517059053779171</v>
+        <v>6.384057848600006</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08667199649463347</v>
+        <v>0.08675699649463348</v>
       </c>
       <c r="C51">
-        <v>60.62473234061467</v>
+        <v>59.39178154608621</v>
       </c>
       <c r="D51">
-        <v>110.9767323406147</v>
+        <v>110.8917815460862</v>
       </c>
       <c r="E51">
-        <v>16.05199999999999</v>
+        <v>17.2</v>
       </c>
       <c r="F51">
-        <v>56.252</v>
+        <v>57.4</v>
       </c>
       <c r="G51">
         <v>5.9</v>
@@ -5463,28 +5463,28 @@
         <v>19.5</v>
       </c>
       <c r="M51">
-        <v>3.0544836</v>
+        <v>3.11682</v>
       </c>
       <c r="N51">
-        <v>16.4455164</v>
+        <v>16.38318</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>16.4455164</v>
+        <v>16.38318</v>
       </c>
       <c r="Q51">
-        <v>19.0455164</v>
+        <v>18.98318</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1177745029306539</v>
+        <v>0.1192139929892669</v>
       </c>
       <c r="T51">
-        <v>1.4029170281903</v>
+        <v>1.430975368754106</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.384057848600006</v>
+        <v>6.256376691628005</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08675699649463348</v>
+        <v>0.08684199649463348</v>
       </c>
       <c r="C52">
-        <v>59.39178154608621</v>
+        <v>58.15896070884433</v>
       </c>
       <c r="D52">
-        <v>110.8917815460862</v>
+        <v>110.8069607088443</v>
       </c>
       <c r="E52">
-        <v>17.2</v>
+        <v>18.348</v>
       </c>
       <c r="F52">
-        <v>57.4</v>
+        <v>58.548</v>
       </c>
       <c r="G52">
         <v>5.9</v>
@@ -5545,28 +5545,28 @@
         <v>19.5</v>
       </c>
       <c r="M52">
-        <v>3.11682</v>
+        <v>3.1791564</v>
       </c>
       <c r="N52">
-        <v>16.38318</v>
+        <v>16.3208436</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>16.38318</v>
+        <v>16.3208436</v>
       </c>
       <c r="Q52">
-        <v>18.98318</v>
+        <v>18.9208436</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1192139929892669</v>
+        <v>0.1207122377441499</v>
       </c>
       <c r="T52">
-        <v>1.430975368754106</v>
+        <v>1.460178947708271</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.256376691628005</v>
+        <v>6.133702638850986</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08684199649463348</v>
+        <v>0.08744699649463347</v>
       </c>
       <c r="C53">
-        <v>58.15896070884433</v>
+        <v>56.41096425624558</v>
       </c>
       <c r="D53">
-        <v>110.8069607088443</v>
+        <v>110.2069642562456</v>
       </c>
       <c r="E53">
-        <v>18.348</v>
+        <v>19.496</v>
       </c>
       <c r="F53">
-        <v>58.548</v>
+        <v>59.696</v>
       </c>
       <c r="G53">
         <v>5.9</v>
@@ -5627,45 +5627,45 @@
         <v>19.5</v>
       </c>
       <c r="M53">
-        <v>3.1791564</v>
+        <v>3.3011888</v>
       </c>
       <c r="N53">
-        <v>16.3208436</v>
+        <v>16.1988112</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>16.3208436</v>
+        <v>16.1988112</v>
       </c>
       <c r="Q53">
-        <v>18.9208436</v>
+        <v>18.7988112</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1207122377441499</v>
+        <v>0.1222729093638197</v>
       </c>
       <c r="T53">
-        <v>1.460178947708271</v>
+        <v>1.490599342452194</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.133702638850986</v>
+        <v>5.906962970430532</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08744699649463347</v>
+        <v>0.08754199649463346</v>
       </c>
       <c r="C54">
-        <v>56.41096425624558</v>
+        <v>55.16933969289725</v>
       </c>
       <c r="D54">
-        <v>110.2069642562456</v>
+        <v>110.1133396928972</v>
       </c>
       <c r="E54">
-        <v>19.496</v>
+        <v>20.644</v>
       </c>
       <c r="F54">
-        <v>59.696</v>
+        <v>60.844</v>
       </c>
       <c r="G54">
         <v>5.9</v>
@@ -5709,28 +5709,28 @@
         <v>19.5</v>
       </c>
       <c r="M54">
-        <v>3.3011888</v>
+        <v>3.3646732</v>
       </c>
       <c r="N54">
-        <v>16.1988112</v>
+        <v>16.1353268</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>16.1988112</v>
+        <v>16.1353268</v>
       </c>
       <c r="Q54">
-        <v>18.7988112</v>
+        <v>18.7353268</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1222729093638197</v>
+        <v>0.1238999925417733</v>
       </c>
       <c r="T54">
-        <v>1.490599342452194</v>
+        <v>1.522314222078836</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.906962970430532</v>
+        <v>5.795510838912974</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08754199649463346</v>
+        <v>0.08763699649463347</v>
       </c>
       <c r="C55">
-        <v>55.16933969289725</v>
+        <v>53.92787406902427</v>
       </c>
       <c r="D55">
-        <v>110.1133396928972</v>
+        <v>110.0198740690243</v>
       </c>
       <c r="E55">
-        <v>20.644</v>
+        <v>21.792</v>
       </c>
       <c r="F55">
-        <v>60.844</v>
+        <v>61.992</v>
       </c>
       <c r="G55">
         <v>5.9</v>
@@ -5791,28 +5791,28 @@
         <v>19.5</v>
       </c>
       <c r="M55">
-        <v>3.3646732</v>
+        <v>3.4281576</v>
       </c>
       <c r="N55">
-        <v>16.1353268</v>
+        <v>16.0718424</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>16.1353268</v>
+        <v>16.0718424</v>
       </c>
       <c r="Q55">
-        <v>18.7353268</v>
+        <v>18.6718424</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1238999925417733</v>
+        <v>0.1255978184665945</v>
       </c>
       <c r="T55">
-        <v>1.522314222078836</v>
+        <v>1.555408009515332</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.795510838912974</v>
+        <v>5.688186564118289</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08763699649463347</v>
+        <v>0.08773199649463348</v>
       </c>
       <c r="C56">
-        <v>53.92787406902427</v>
+        <v>52.68656698024036</v>
       </c>
       <c r="D56">
-        <v>110.0198740690243</v>
+        <v>109.9265669802404</v>
       </c>
       <c r="E56">
-        <v>21.792</v>
+        <v>22.94</v>
       </c>
       <c r="F56">
-        <v>61.992</v>
+        <v>63.14</v>
       </c>
       <c r="G56">
         <v>5.9</v>
@@ -5873,28 +5873,28 @@
         <v>19.5</v>
       </c>
       <c r="M56">
-        <v>3.4281576</v>
+        <v>3.491642</v>
       </c>
       <c r="N56">
-        <v>16.0718424</v>
+        <v>16.008358</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>16.0718424</v>
+        <v>16.008358</v>
       </c>
       <c r="Q56">
-        <v>18.6718424</v>
+        <v>18.608358</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1255978184665945</v>
+        <v>0.1273711033214077</v>
       </c>
       <c r="T56">
-        <v>1.555408009515332</v>
+        <v>1.589972631949007</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.688186564118289</v>
+        <v>5.58476499022523</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08773199649463348</v>
+        <v>0.08782699649463346</v>
       </c>
       <c r="C57">
-        <v>52.68656698024036</v>
+        <v>51.44541802352974</v>
       </c>
       <c r="D57">
-        <v>109.9265669802404</v>
+        <v>109.8334180235297</v>
       </c>
       <c r="E57">
-        <v>22.94</v>
+        <v>24.08800000000001</v>
       </c>
       <c r="F57">
-        <v>63.14</v>
+        <v>64.28800000000001</v>
       </c>
       <c r="G57">
         <v>5.9</v>
@@ -5955,28 +5955,28 @@
         <v>19.5</v>
       </c>
       <c r="M57">
-        <v>3.491642</v>
+        <v>3.555126400000001</v>
       </c>
       <c r="N57">
-        <v>16.008358</v>
+        <v>15.9448736</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>16.008358</v>
+        <v>15.9448736</v>
       </c>
       <c r="Q57">
-        <v>18.608358</v>
+        <v>18.5448736</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1273711033214077</v>
+        <v>0.1292249920332579</v>
       </c>
       <c r="T57">
-        <v>1.589972631949007</v>
+        <v>1.626108373584211</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.58476499022523</v>
+        <v>5.485037043971206</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08782699649463346</v>
+        <v>0.08792199649463348</v>
       </c>
       <c r="C58">
-        <v>51.44541802352974</v>
+        <v>50.20442679724154</v>
       </c>
       <c r="D58">
-        <v>109.8334180235297</v>
+        <v>109.7404267972415</v>
       </c>
       <c r="E58">
-        <v>24.08800000000001</v>
+        <v>25.236</v>
       </c>
       <c r="F58">
-        <v>64.28800000000001</v>
+        <v>65.43600000000001</v>
       </c>
       <c r="G58">
         <v>5.9</v>
@@ -6037,28 +6037,28 @@
         <v>19.5</v>
       </c>
       <c r="M58">
-        <v>3.555126400000001</v>
+        <v>3.6186108</v>
       </c>
       <c r="N58">
-        <v>15.9448736</v>
+        <v>15.8813892</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>15.9448736</v>
+        <v>15.8813892</v>
       </c>
       <c r="Q58">
-        <v>18.5448736</v>
+        <v>18.4813892</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1292249920332579</v>
+        <v>0.1311651081270546</v>
       </c>
       <c r="T58">
-        <v>1.626108373584211</v>
+        <v>1.663924847388496</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.485037043971206</v>
+        <v>5.388808323901537</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08792199649463348</v>
+        <v>0.08801699649463346</v>
       </c>
       <c r="C59">
-        <v>50.20442679724154</v>
+        <v>48.96359290108408</v>
       </c>
       <c r="D59">
-        <v>109.7404267972415</v>
+        <v>109.6475929010841</v>
       </c>
       <c r="E59">
-        <v>25.236</v>
+        <v>26.384</v>
       </c>
       <c r="F59">
-        <v>65.43600000000001</v>
+        <v>66.584</v>
       </c>
       <c r="G59">
         <v>5.9</v>
@@ -6119,28 +6119,28 @@
         <v>19.5</v>
       </c>
       <c r="M59">
-        <v>3.6186108</v>
+        <v>3.6820952</v>
       </c>
       <c r="N59">
-        <v>15.8813892</v>
+        <v>15.8179048</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>15.8813892</v>
+        <v>15.8179048</v>
       </c>
       <c r="Q59">
-        <v>18.4813892</v>
+        <v>18.4179048</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1311651081270546</v>
+        <v>0.1331976107015083</v>
       </c>
       <c r="T59">
-        <v>1.663924847388496</v>
+        <v>1.70354210565965</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.388808323901537</v>
+        <v>5.295897835558407</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08801699649463346</v>
+        <v>0.08811199649463347</v>
       </c>
       <c r="C60">
-        <v>48.9635929010841</v>
+        <v>47.72291593611885</v>
       </c>
       <c r="D60">
-        <v>109.6475929010841</v>
+        <v>109.5549159361188</v>
       </c>
       <c r="E60">
-        <v>26.38399999999999</v>
+        <v>27.532</v>
       </c>
       <c r="F60">
-        <v>66.58399999999999</v>
+        <v>67.732</v>
       </c>
       <c r="G60">
         <v>5.9</v>
@@ -6201,28 +6201,28 @@
         <v>19.5</v>
       </c>
       <c r="M60">
-        <v>3.6820952</v>
+        <v>3.7455796</v>
       </c>
       <c r="N60">
-        <v>15.8179048</v>
+        <v>15.7544204</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>15.8179048</v>
+        <v>15.7544204</v>
       </c>
       <c r="Q60">
-        <v>18.4179048</v>
+        <v>18.3544204</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1331976107015082</v>
+        <v>0.1353292597430084</v>
       </c>
       <c r="T60">
-        <v>1.703542105659649</v>
+        <v>1.745091913114763</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.295897835558407</v>
+        <v>5.206136855294705</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08811199649463347</v>
+        <v>0.08820699649463348</v>
       </c>
       <c r="C61">
-        <v>47.72291593611885</v>
+        <v>46.48239550475512</v>
       </c>
       <c r="D61">
-        <v>109.5549159361188</v>
+        <v>109.4623955047551</v>
       </c>
       <c r="E61">
-        <v>27.532</v>
+        <v>28.67999999999999</v>
       </c>
       <c r="F61">
-        <v>67.732</v>
+        <v>68.88</v>
       </c>
       <c r="G61">
         <v>5.9</v>
@@ -6283,28 +6283,28 @@
         <v>19.5</v>
       </c>
       <c r="M61">
-        <v>3.7455796</v>
+        <v>3.809064</v>
       </c>
       <c r="N61">
-        <v>15.7544204</v>
+        <v>15.690936</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>15.7544204</v>
+        <v>15.690936</v>
       </c>
       <c r="Q61">
-        <v>18.3544204</v>
+        <v>18.290936</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1353292597430084</v>
+        <v>0.1375674912365837</v>
       </c>
       <c r="T61">
-        <v>1.745091913114763</v>
+        <v>1.788719210942632</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.206136855294705</v>
+        <v>5.119367907706461</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08820699649463348</v>
+        <v>0.08830199649463347</v>
       </c>
       <c r="C62">
-        <v>46.48239550475512</v>
+        <v>45.24203121074406</v>
       </c>
       <c r="D62">
-        <v>109.4623955047551</v>
+        <v>109.370031210744</v>
       </c>
       <c r="E62">
-        <v>28.67999999999999</v>
+        <v>29.82799999999999</v>
       </c>
       <c r="F62">
-        <v>68.88</v>
+        <v>70.02799999999999</v>
       </c>
       <c r="G62">
         <v>5.9</v>
@@ -6365,28 +6365,28 @@
         <v>19.5</v>
       </c>
       <c r="M62">
-        <v>3.809064</v>
+        <v>3.8725484</v>
       </c>
       <c r="N62">
-        <v>15.690936</v>
+        <v>15.6274516</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>15.690936</v>
+        <v>15.6274516</v>
       </c>
       <c r="Q62">
-        <v>18.290936</v>
+        <v>18.2274516</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1375674912365837</v>
+        <v>0.1399205038323935</v>
       </c>
       <c r="T62">
-        <v>1.788719210942632</v>
+        <v>1.834583806095007</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.119367907706461</v>
+        <v>5.035443843645699</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08830199649463347</v>
+        <v>0.08839699649463348</v>
       </c>
       <c r="C63">
-        <v>45.24203121074406</v>
+        <v>44.00182265917307</v>
       </c>
       <c r="D63">
-        <v>109.370031210744</v>
+        <v>109.2778226591731</v>
       </c>
       <c r="E63">
-        <v>29.82799999999999</v>
+        <v>30.976</v>
       </c>
       <c r="F63">
-        <v>70.02799999999999</v>
+        <v>71.176</v>
       </c>
       <c r="G63">
         <v>5.9</v>
@@ -6447,28 +6447,28 @@
         <v>19.5</v>
       </c>
       <c r="M63">
-        <v>3.8725484</v>
+        <v>3.9360328</v>
       </c>
       <c r="N63">
-        <v>15.6274516</v>
+        <v>15.5639672</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>15.6274516</v>
+        <v>15.5639672</v>
       </c>
       <c r="Q63">
-        <v>18.2274516</v>
+        <v>18.1639672</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1399205038323935</v>
+        <v>0.1423973591964039</v>
       </c>
       <c r="T63">
-        <v>1.834583806095007</v>
+        <v>1.882862327308034</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.035443843645699</v>
+        <v>4.954227007457865</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08839699649463348</v>
+        <v>0.08849199649463346</v>
       </c>
       <c r="C64">
-        <v>44.00182265917307</v>
+        <v>42.76176945646033</v>
       </c>
       <c r="D64">
-        <v>109.2778226591731</v>
+        <v>109.1857694564603</v>
       </c>
       <c r="E64">
-        <v>30.976</v>
+        <v>32.124</v>
       </c>
       <c r="F64">
-        <v>71.176</v>
+        <v>72.324</v>
       </c>
       <c r="G64">
         <v>5.9</v>
@@ -6529,28 +6529,28 @@
         <v>19.5</v>
       </c>
       <c r="M64">
-        <v>3.9360328</v>
+        <v>3.9995172</v>
       </c>
       <c r="N64">
-        <v>15.5639672</v>
+        <v>15.5004828</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>15.5639672</v>
+        <v>15.5004828</v>
       </c>
       <c r="Q64">
-        <v>18.1639672</v>
+        <v>18.1004828</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1423973591964039</v>
+        <v>0.1450080986341445</v>
       </c>
       <c r="T64">
-        <v>1.882862327308034</v>
+        <v>1.933750498316359</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.954227007457865</v>
+        <v>4.875588483529961</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08849199649463346</v>
+        <v>0.08858699649463347</v>
       </c>
       <c r="C65">
-        <v>42.76176945646033</v>
+        <v>41.52187121034899</v>
       </c>
       <c r="D65">
-        <v>109.1857694564603</v>
+        <v>109.093871210349</v>
       </c>
       <c r="E65">
-        <v>32.124</v>
+        <v>33.27199999999999</v>
       </c>
       <c r="F65">
-        <v>72.324</v>
+        <v>73.47199999999999</v>
       </c>
       <c r="G65">
         <v>5.9</v>
@@ -6611,28 +6611,28 @@
         <v>19.5</v>
       </c>
       <c r="M65">
-        <v>3.9995172</v>
+        <v>4.0630016</v>
       </c>
       <c r="N65">
-        <v>15.5004828</v>
+        <v>15.4369984</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>15.5004828</v>
+        <v>15.4369984</v>
       </c>
       <c r="Q65">
-        <v>18.1004828</v>
+        <v>18.0369984</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1450080986341445</v>
+        <v>0.1477638791517596</v>
       </c>
       <c r="T65">
-        <v>1.933750498316359</v>
+        <v>1.987465789936258</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.875588483529961</v>
+        <v>4.799407413474807</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08858699649463347</v>
+        <v>0.08868199649463347</v>
       </c>
       <c r="C66">
-        <v>41.52187121034899</v>
+        <v>40.28212752990171</v>
       </c>
       <c r="D66">
-        <v>109.093871210349</v>
+        <v>109.0021275299017</v>
       </c>
       <c r="E66">
-        <v>33.27199999999999</v>
+        <v>34.42</v>
       </c>
       <c r="F66">
-        <v>73.47199999999999</v>
+        <v>74.62</v>
       </c>
       <c r="G66">
         <v>5.9</v>
@@ -6693,28 +6693,28 @@
         <v>19.5</v>
       </c>
       <c r="M66">
-        <v>4.0630016</v>
+        <v>4.126486000000001</v>
       </c>
       <c r="N66">
-        <v>15.4369984</v>
+        <v>15.373514</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>15.4369984</v>
+        <v>15.373514</v>
       </c>
       <c r="Q66">
-        <v>18.0369984</v>
+        <v>17.973514</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1477638791517596</v>
+        <v>0.1506771328418099</v>
       </c>
       <c r="T66">
-        <v>1.987465789936258</v>
+        <v>2.04425052679158</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.799407413474807</v>
+        <v>4.725570376344423</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08868199649463347</v>
+        <v>0.08877699649463347</v>
       </c>
       <c r="C67">
-        <v>40.28212752990171</v>
+        <v>39.04253802549513</v>
       </c>
       <c r="D67">
-        <v>109.0021275299017</v>
+        <v>108.9105380254951</v>
       </c>
       <c r="E67">
-        <v>34.42</v>
+        <v>35.568</v>
       </c>
       <c r="F67">
-        <v>74.62</v>
+        <v>75.768</v>
       </c>
       <c r="G67">
         <v>5.9</v>
@@ -6775,28 +6775,28 @@
         <v>19.5</v>
       </c>
       <c r="M67">
-        <v>4.126486000000001</v>
+        <v>4.1899704</v>
       </c>
       <c r="N67">
-        <v>15.373514</v>
+        <v>15.3100296</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>15.373514</v>
+        <v>15.3100296</v>
       </c>
       <c r="Q67">
-        <v>17.973514</v>
+        <v>17.9100296</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1506771328418099</v>
+        <v>0.1537617543959808</v>
       </c>
       <c r="T67">
-        <v>2.04425052679158</v>
+        <v>2.10437554228545</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.725570376344423</v>
+        <v>4.653970825187692</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08877699649463347</v>
+        <v>0.08887199649463347</v>
       </c>
       <c r="C68">
-        <v>39.04253802549513</v>
+        <v>37.80310230881429</v>
       </c>
       <c r="D68">
-        <v>108.9105380254951</v>
+        <v>108.8191023088143</v>
       </c>
       <c r="E68">
-        <v>35.568</v>
+        <v>36.71599999999999</v>
       </c>
       <c r="F68">
-        <v>75.768</v>
+        <v>76.916</v>
       </c>
       <c r="G68">
         <v>5.9</v>
@@ -6857,28 +6857,28 @@
         <v>19.5</v>
       </c>
       <c r="M68">
-        <v>4.1899704</v>
+        <v>4.2534548</v>
       </c>
       <c r="N68">
-        <v>15.3100296</v>
+        <v>15.2465452</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>15.3100296</v>
+        <v>15.2465452</v>
       </c>
       <c r="Q68">
-        <v>17.9100296</v>
+        <v>17.8465452</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1537617543959808</v>
+        <v>0.1570333227110105</v>
       </c>
       <c r="T68">
-        <v>2.10437554228545</v>
+        <v>2.168144498112282</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.653970825187692</v>
+        <v>4.584508574065486</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08887199649463347</v>
+        <v>0.08896699649463348</v>
       </c>
       <c r="C69">
-        <v>37.80310230881429</v>
+        <v>36.56381999284714</v>
       </c>
       <c r="D69">
-        <v>108.8191023088143</v>
+        <v>108.7278199928471</v>
       </c>
       <c r="E69">
-        <v>36.71599999999999</v>
+        <v>37.864</v>
       </c>
       <c r="F69">
-        <v>76.916</v>
+        <v>78.06400000000001</v>
       </c>
       <c r="G69">
         <v>5.9</v>
@@ -6939,28 +6939,28 @@
         <v>19.5</v>
       </c>
       <c r="M69">
-        <v>4.2534548</v>
+        <v>4.3169392</v>
       </c>
       <c r="N69">
-        <v>15.2465452</v>
+        <v>15.1830608</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>15.2465452</v>
+        <v>15.1830608</v>
       </c>
       <c r="Q69">
-        <v>17.8465452</v>
+        <v>17.7830608</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1570333227110105</v>
+        <v>0.1605093640457296</v>
       </c>
       <c r="T69">
-        <v>2.168144498112282</v>
+        <v>2.235899013678291</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.584508574065486</v>
+        <v>4.517089330329229</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08896699649463348</v>
+        <v>0.09078699649463348</v>
       </c>
       <c r="C70">
-        <v>36.56381999284714</v>
+        <v>33.69614595984584</v>
       </c>
       <c r="D70">
-        <v>108.7278199928471</v>
+        <v>107.0081459598458</v>
       </c>
       <c r="E70">
-        <v>37.864</v>
+        <v>39.012</v>
       </c>
       <c r="F70">
-        <v>78.06400000000001</v>
+        <v>79.212</v>
       </c>
       <c r="G70">
         <v>5.9</v>
@@ -7021,45 +7021,45 @@
         <v>19.5</v>
       </c>
       <c r="M70">
-        <v>4.3169392</v>
+        <v>4.5784536</v>
       </c>
       <c r="N70">
-        <v>15.1830608</v>
+        <v>14.9215464</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>15.1830608</v>
+        <v>14.9215464</v>
       </c>
       <c r="Q70">
-        <v>17.7830608</v>
+        <v>17.5215464</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1605093640457296</v>
+        <v>0.1642096661117209</v>
       </c>
       <c r="T70">
-        <v>2.235899013678291</v>
+        <v>2.308024788313074</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.517089330329229</v>
+        <v>4.259079965340263</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09078699649463348</v>
+        <v>0.09090699649463346</v>
       </c>
       <c r="C71">
-        <v>33.69614595984584</v>
+        <v>32.43667044434372</v>
       </c>
       <c r="D71">
-        <v>107.0081459598458</v>
+        <v>106.8966704443437</v>
       </c>
       <c r="E71">
-        <v>39.012</v>
+        <v>40.16</v>
       </c>
       <c r="F71">
-        <v>79.212</v>
+        <v>80.36</v>
       </c>
       <c r="G71">
         <v>5.9</v>
@@ -7103,28 +7103,28 @@
         <v>19.5</v>
       </c>
       <c r="M71">
-        <v>4.5784536</v>
+        <v>4.644808</v>
       </c>
       <c r="N71">
-        <v>14.9215464</v>
+        <v>14.855192</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>14.9215464</v>
+        <v>14.855192</v>
       </c>
       <c r="Q71">
-        <v>17.5215464</v>
+        <v>17.455192</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1642096661117209</v>
+        <v>0.1681566549821116</v>
       </c>
       <c r="T71">
-        <v>2.308024788313074</v>
+        <v>2.38495894792351</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.259079965340263</v>
+        <v>4.198235965835401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09090699649463346</v>
+        <v>0.09102699649463347</v>
       </c>
       <c r="C72">
-        <v>32.43667044434372</v>
+        <v>31.17742694591526</v>
       </c>
       <c r="D72">
-        <v>106.8966704443437</v>
+        <v>106.7854269459153</v>
       </c>
       <c r="E72">
-        <v>40.16</v>
+        <v>41.30800000000001</v>
       </c>
       <c r="F72">
-        <v>80.36</v>
+        <v>81.50800000000001</v>
       </c>
       <c r="G72">
         <v>5.9</v>
@@ -7185,28 +7185,28 @@
         <v>19.5</v>
       </c>
       <c r="M72">
-        <v>4.644808</v>
+        <v>4.711162400000001</v>
       </c>
       <c r="N72">
-        <v>14.855192</v>
+        <v>14.7888376</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>14.855192</v>
+        <v>14.7888376</v>
       </c>
       <c r="Q72">
-        <v>17.455192</v>
+        <v>17.3888376</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1681566549821116</v>
+        <v>0.1723758499814948</v>
       </c>
       <c r="T72">
-        <v>2.38495894792351</v>
+        <v>2.467198911645011</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.198235965835401</v>
+        <v>4.139105881809551</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09102699649463347</v>
+        <v>0.09114699649463348</v>
       </c>
       <c r="C73">
-        <v>31.17742694591527</v>
+        <v>29.91841474095827</v>
       </c>
       <c r="D73">
-        <v>106.7854269459153</v>
+        <v>106.6744147409583</v>
       </c>
       <c r="E73">
-        <v>41.30799999999999</v>
+        <v>42.45599999999999</v>
       </c>
       <c r="F73">
-        <v>81.508</v>
+        <v>82.65599999999999</v>
       </c>
       <c r="G73">
         <v>5.9</v>
@@ -7267,28 +7267,28 @@
         <v>19.5</v>
       </c>
       <c r="M73">
-        <v>4.7111624</v>
+        <v>4.7775168</v>
       </c>
       <c r="N73">
-        <v>14.7888376</v>
+        <v>14.7224832</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>14.7888376</v>
+        <v>14.7224832</v>
       </c>
       <c r="Q73">
-        <v>17.3888376</v>
+        <v>17.3224832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1723758499814947</v>
+        <v>0.1768964160522624</v>
       </c>
       <c r="T73">
-        <v>2.46719891164501</v>
+        <v>2.555313158489474</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.139105881809551</v>
+        <v>4.081618300117752</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09114699649463348</v>
+        <v>0.09126699649463346</v>
       </c>
       <c r="C74">
-        <v>29.91841474095827</v>
+        <v>28.65963310887624</v>
       </c>
       <c r="D74">
-        <v>106.6744147409583</v>
+        <v>106.5636331088762</v>
       </c>
       <c r="E74">
-        <v>42.45599999999999</v>
+        <v>43.604</v>
       </c>
       <c r="F74">
-        <v>82.65599999999999</v>
+        <v>83.804</v>
       </c>
       <c r="G74">
         <v>5.9</v>
@@ -7349,28 +7349,28 @@
         <v>19.5</v>
       </c>
       <c r="M74">
-        <v>4.7775168</v>
+        <v>4.843871200000001</v>
       </c>
       <c r="N74">
-        <v>14.7224832</v>
+        <v>14.6561288</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>14.7224832</v>
+        <v>14.6561288</v>
       </c>
       <c r="Q74">
-        <v>17.3224832</v>
+        <v>17.2561288</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1768964160522624</v>
+        <v>0.1817518388690128</v>
       </c>
       <c r="T74">
-        <v>2.555313158489474</v>
+        <v>2.649954386581677</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.081618300117752</v>
+        <v>4.025705720664083</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09126699649463346</v>
+        <v>0.09397699649463348</v>
       </c>
       <c r="C75">
-        <v>28.65963310887624</v>
+        <v>25.06968339713268</v>
       </c>
       <c r="D75">
-        <v>106.5636331088762</v>
+        <v>104.1216833971327</v>
       </c>
       <c r="E75">
-        <v>43.604</v>
+        <v>44.752</v>
       </c>
       <c r="F75">
-        <v>83.804</v>
+        <v>84.952</v>
       </c>
       <c r="G75">
         <v>5.9</v>
@@ -7431,45 +7431,45 @@
         <v>19.5</v>
       </c>
       <c r="M75">
-        <v>4.843871200000001</v>
+        <v>5.2075576</v>
       </c>
       <c r="N75">
-        <v>14.6561288</v>
+        <v>14.2924424</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>14.6561288</v>
+        <v>14.2924424</v>
       </c>
       <c r="Q75">
-        <v>17.2561288</v>
+        <v>16.8924424</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1817518388690128</v>
+        <v>0.1869807557485903</v>
       </c>
       <c r="T75">
-        <v>2.649954386581677</v>
+        <v>2.751875709142511</v>
       </c>
       <c r="U75">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.025705720664083</v>
+        <v>3.744557717422079</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09397699649463348</v>
+        <v>0.09413199649463347</v>
       </c>
       <c r="C76">
-        <v>25.06968339713268</v>
+        <v>23.78539388216892</v>
       </c>
       <c r="D76">
-        <v>104.1216833971327</v>
+        <v>103.9853938821689</v>
       </c>
       <c r="E76">
-        <v>44.752</v>
+        <v>45.89999999999999</v>
       </c>
       <c r="F76">
-        <v>84.952</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G76">
         <v>5.9</v>
@@ -7513,28 +7513,28 @@
         <v>19.5</v>
       </c>
       <c r="M76">
-        <v>5.2075576</v>
+        <v>5.27793</v>
       </c>
       <c r="N76">
-        <v>14.2924424</v>
+        <v>14.22207</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>14.2924424</v>
+        <v>14.22207</v>
       </c>
       <c r="Q76">
-        <v>16.8924424</v>
+        <v>16.82207</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1869807557485903</v>
+        <v>0.1926279859785339</v>
       </c>
       <c r="T76">
-        <v>2.751875709142511</v>
+        <v>2.861950737508212</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.744557717422079</v>
+        <v>3.694630281189785</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09413199649463347</v>
+        <v>0.09428699649463347</v>
       </c>
       <c r="C77">
-        <v>23.78539388216892</v>
+        <v>22.50146069164478</v>
       </c>
       <c r="D77">
-        <v>103.9853938821689</v>
+        <v>103.8494606916448</v>
       </c>
       <c r="E77">
-        <v>45.89999999999999</v>
+        <v>47.048</v>
       </c>
       <c r="F77">
-        <v>86.09999999999999</v>
+        <v>87.248</v>
       </c>
       <c r="G77">
         <v>5.9</v>
@@ -7595,28 +7595,28 @@
         <v>19.5</v>
       </c>
       <c r="M77">
-        <v>5.27793</v>
+        <v>5.348302400000001</v>
       </c>
       <c r="N77">
-        <v>14.22207</v>
+        <v>14.1516976</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>14.22207</v>
+        <v>14.1516976</v>
       </c>
       <c r="Q77">
-        <v>16.82207</v>
+        <v>16.7516976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1926279859785339</v>
+        <v>0.1987458187276395</v>
       </c>
       <c r="T77">
-        <v>2.861950737508212</v>
+        <v>2.981198684904387</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.694630281189785</v>
+        <v>3.646016724858339</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09428699649463347</v>
+        <v>0.09444199649463347</v>
       </c>
       <c r="C78">
-        <v>22.50146069164478</v>
+        <v>21.21788242998694</v>
       </c>
       <c r="D78">
-        <v>103.8494606916448</v>
+        <v>103.7138824299869</v>
       </c>
       <c r="E78">
-        <v>47.048</v>
+        <v>48.196</v>
       </c>
       <c r="F78">
-        <v>87.248</v>
+        <v>88.396</v>
       </c>
       <c r="G78">
         <v>5.9</v>
@@ -7677,28 +7677,28 @@
         <v>19.5</v>
       </c>
       <c r="M78">
-        <v>5.348302400000001</v>
+        <v>5.4186748</v>
       </c>
       <c r="N78">
-        <v>14.1516976</v>
+        <v>14.0813252</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>14.1516976</v>
+        <v>14.0813252</v>
       </c>
       <c r="Q78">
-        <v>16.7516976</v>
+        <v>16.6813252</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1987458187276395</v>
+        <v>0.205395636933189</v>
       </c>
       <c r="T78">
-        <v>2.981198684904387</v>
+        <v>3.110816019030664</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.646016724858339</v>
+        <v>3.598665858301739</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09444199649463347</v>
+        <v>0.09459699649463346</v>
       </c>
       <c r="C79">
-        <v>21.21788242998694</v>
+        <v>19.93465770890032</v>
       </c>
       <c r="D79">
-        <v>103.7138824299869</v>
+        <v>103.5786577089003</v>
       </c>
       <c r="E79">
-        <v>48.196</v>
+        <v>49.34399999999999</v>
       </c>
       <c r="F79">
-        <v>88.396</v>
+        <v>89.544</v>
       </c>
       <c r="G79">
         <v>5.9</v>
@@ -7759,28 +7759,28 @@
         <v>19.5</v>
       </c>
       <c r="M79">
-        <v>5.4186748</v>
+        <v>5.4890472</v>
       </c>
       <c r="N79">
-        <v>14.0813252</v>
+        <v>14.0109528</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>14.0813252</v>
+        <v>14.0109528</v>
       </c>
       <c r="Q79">
-        <v>16.6813252</v>
+        <v>16.6109528</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.205395636933189</v>
+        <v>0.2126499840665158</v>
       </c>
       <c r="T79">
-        <v>3.110816019030664</v>
+        <v>3.252216747168422</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.598665858301739</v>
+        <v>3.552529116528639</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09459699649463346</v>
+        <v>0.09475199649463348</v>
       </c>
       <c r="C80">
-        <v>19.93465770890032</v>
+        <v>18.65178514732074</v>
       </c>
       <c r="D80">
-        <v>103.5786577089003</v>
+        <v>103.4437851473207</v>
       </c>
       <c r="E80">
-        <v>49.34399999999999</v>
+        <v>50.492</v>
       </c>
       <c r="F80">
-        <v>89.544</v>
+        <v>90.69200000000001</v>
       </c>
       <c r="G80">
         <v>5.9</v>
@@ -7841,28 +7841,28 @@
         <v>19.5</v>
       </c>
       <c r="M80">
-        <v>5.4890472</v>
+        <v>5.559419600000001</v>
       </c>
       <c r="N80">
-        <v>14.0109528</v>
+        <v>13.9405804</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>14.0109528</v>
+        <v>13.9405804</v>
       </c>
       <c r="Q80">
-        <v>16.6109528</v>
+        <v>16.5405804</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2126499840665158</v>
+        <v>0.2205952214030165</v>
       </c>
       <c r="T80">
-        <v>3.252216747168422</v>
+        <v>3.4070842113193</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.552529116528639</v>
+        <v>3.507560393534605</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09475199649463348</v>
+        <v>0.09714699649463347</v>
       </c>
       <c r="C81">
-        <v>18.65178514732074</v>
+        <v>15.46354962557859</v>
       </c>
       <c r="D81">
-        <v>103.4437851473207</v>
+        <v>101.4035496255786</v>
       </c>
       <c r="E81">
-        <v>50.492</v>
+        <v>51.64</v>
       </c>
       <c r="F81">
-        <v>90.69200000000001</v>
+        <v>91.84</v>
       </c>
       <c r="G81">
         <v>5.9</v>
@@ -7923,45 +7923,45 @@
         <v>19.5</v>
       </c>
       <c r="M81">
-        <v>5.559419600000001</v>
+        <v>5.886944000000001</v>
       </c>
       <c r="N81">
-        <v>13.9405804</v>
+        <v>13.613056</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>13.9405804</v>
+        <v>13.613056</v>
       </c>
       <c r="Q81">
-        <v>16.5405804</v>
+        <v>16.213056</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2205952214030165</v>
+        <v>0.2293349824731674</v>
       </c>
       <c r="T81">
-        <v>3.4070842113193</v>
+        <v>3.577438421885265</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.507560393534605</v>
+        <v>3.312414726554219</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09714699649463347</v>
+        <v>0.09732999649463348</v>
       </c>
       <c r="C82">
-        <v>15.46354962557859</v>
+        <v>14.16296153824595</v>
       </c>
       <c r="D82">
-        <v>101.4035496255786</v>
+        <v>101.2509615382459</v>
       </c>
       <c r="E82">
-        <v>51.64</v>
+        <v>52.788</v>
       </c>
       <c r="F82">
-        <v>91.84</v>
+        <v>92.988</v>
       </c>
       <c r="G82">
         <v>5.9</v>
@@ -8005,28 +8005,28 @@
         <v>19.5</v>
       </c>
       <c r="M82">
-        <v>5.886944000000001</v>
+        <v>5.960530800000001</v>
       </c>
       <c r="N82">
-        <v>13.613056</v>
+        <v>13.5394692</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>13.613056</v>
+        <v>13.5394692</v>
       </c>
       <c r="Q82">
-        <v>16.213056</v>
+        <v>16.1394692</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2293349824731674</v>
+        <v>0.2389947183928078</v>
       </c>
       <c r="T82">
-        <v>3.577438421885265</v>
+        <v>3.765724654616069</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.312414726554219</v>
+        <v>3.271520717584413</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09732999649463348</v>
+        <v>0.09751299649463346</v>
       </c>
       <c r="C83">
-        <v>14.16296153824595</v>
+        <v>12.86283197808694</v>
       </c>
       <c r="D83">
-        <v>101.2509615382459</v>
+        <v>101.0988319780869</v>
       </c>
       <c r="E83">
-        <v>52.788</v>
+        <v>53.93600000000001</v>
       </c>
       <c r="F83">
-        <v>92.988</v>
+        <v>94.13600000000001</v>
       </c>
       <c r="G83">
         <v>5.9</v>
@@ -8087,28 +8087,28 @@
         <v>19.5</v>
       </c>
       <c r="M83">
-        <v>5.960530800000001</v>
+        <v>6.034117600000001</v>
       </c>
       <c r="N83">
-        <v>13.5394692</v>
+        <v>13.4658824</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>13.5394692</v>
+        <v>13.4658824</v>
       </c>
       <c r="Q83">
-        <v>16.1394692</v>
+        <v>16.0658824</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2389947183928078</v>
+        <v>0.2497277583035193</v>
       </c>
       <c r="T83">
-        <v>3.765724654616069</v>
+        <v>3.974931579872517</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.271520717584413</v>
+        <v>3.23162412346753</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09751299649463346</v>
+        <v>0.09769599649463348</v>
       </c>
       <c r="C84">
-        <v>12.86283197808694</v>
+        <v>11.56315888139117</v>
       </c>
       <c r="D84">
-        <v>101.0988319780869</v>
+        <v>100.9471588813912</v>
       </c>
       <c r="E84">
-        <v>53.93600000000001</v>
+        <v>55.084</v>
       </c>
       <c r="F84">
-        <v>94.13600000000001</v>
+        <v>95.28400000000001</v>
       </c>
       <c r="G84">
         <v>5.9</v>
@@ -8169,28 +8169,28 @@
         <v>19.5</v>
       </c>
       <c r="M84">
-        <v>6.034117600000001</v>
+        <v>6.107704400000001</v>
       </c>
       <c r="N84">
-        <v>13.4658824</v>
+        <v>13.3922956</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>13.4658824</v>
+        <v>13.3922956</v>
       </c>
       <c r="Q84">
-        <v>16.0658824</v>
+        <v>15.9922956</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2497277583035193</v>
+        <v>0.2617235087919617</v>
       </c>
       <c r="T84">
-        <v>3.974931579872517</v>
+        <v>4.208751084570901</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.23162412346753</v>
+        <v>3.192688893064307</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09769599649463348</v>
+        <v>0.09787899649463347</v>
       </c>
       <c r="C85">
-        <v>11.56315888139117</v>
+        <v>10.26394019681408</v>
       </c>
       <c r="D85">
-        <v>100.9471588813912</v>
+        <v>100.7959401968141</v>
       </c>
       <c r="E85">
-        <v>55.084</v>
+        <v>56.232</v>
       </c>
       <c r="F85">
-        <v>95.28400000000001</v>
+        <v>96.432</v>
       </c>
       <c r="G85">
         <v>5.9</v>
@@ -8251,28 +8251,28 @@
         <v>19.5</v>
       </c>
       <c r="M85">
-        <v>6.107704400000001</v>
+        <v>6.1812912</v>
       </c>
       <c r="N85">
-        <v>13.3922956</v>
+        <v>13.3187088</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>13.3922956</v>
+        <v>13.3187088</v>
       </c>
       <c r="Q85">
-        <v>15.9922956</v>
+        <v>15.9187088</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2617235087919617</v>
+        <v>0.2752187280914593</v>
       </c>
       <c r="T85">
-        <v>4.208751084570901</v>
+        <v>4.471798027356583</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.192688893064307</v>
+        <v>3.154680691956399</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09787899649463347</v>
+        <v>0.09806199649463347</v>
       </c>
       <c r="C86">
-        <v>10.26394019681409</v>
+        <v>8.965173885284187</v>
       </c>
       <c r="D86">
-        <v>100.7959401968141</v>
+        <v>100.6451738852842</v>
       </c>
       <c r="E86">
-        <v>56.23199999999999</v>
+        <v>57.38</v>
       </c>
       <c r="F86">
-        <v>96.43199999999999</v>
+        <v>97.58</v>
       </c>
       <c r="G86">
         <v>5.9</v>
@@ -8333,28 +8333,28 @@
         <v>19.5</v>
       </c>
       <c r="M86">
-        <v>6.1812912</v>
+        <v>6.254878000000001</v>
       </c>
       <c r="N86">
-        <v>13.3187088</v>
+        <v>13.245122</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>13.3187088</v>
+        <v>13.245122</v>
       </c>
       <c r="Q86">
-        <v>15.9187088</v>
+        <v>15.845122</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2752187280914591</v>
+        <v>0.2905133099642231</v>
       </c>
       <c r="T86">
-        <v>4.47179802735658</v>
+        <v>4.769917895847019</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.154680691956399</v>
+        <v>3.117566801462794</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09806199649463347</v>
+        <v>0.09824499649463347</v>
       </c>
       <c r="C87">
-        <v>8.965173885284187</v>
+        <v>7.666857919911777</v>
       </c>
       <c r="D87">
-        <v>100.6451738852842</v>
+        <v>100.4948579199118</v>
       </c>
       <c r="E87">
-        <v>57.38</v>
+        <v>58.52799999999999</v>
       </c>
       <c r="F87">
-        <v>97.58</v>
+        <v>98.72799999999999</v>
       </c>
       <c r="G87">
         <v>5.9</v>
@@ -8415,28 +8415,28 @@
         <v>19.5</v>
       </c>
       <c r="M87">
-        <v>6.254878000000001</v>
+        <v>6.3284648</v>
       </c>
       <c r="N87">
-        <v>13.245122</v>
+        <v>13.1715352</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>13.245122</v>
+        <v>13.1715352</v>
       </c>
       <c r="Q87">
-        <v>15.845122</v>
+        <v>15.7715352</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2905133099642231</v>
+        <v>0.3079928321045248</v>
       </c>
       <c r="T87">
-        <v>4.769917895847019</v>
+        <v>5.110626316978949</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.117566801462794</v>
+        <v>3.081316024701599</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09824499649463347</v>
+        <v>0.09842799649463348</v>
       </c>
       <c r="C88">
-        <v>7.666857919911777</v>
+        <v>6.368990285897809</v>
       </c>
       <c r="D88">
-        <v>100.4948579199118</v>
+        <v>100.3449902858978</v>
       </c>
       <c r="E88">
-        <v>58.52799999999999</v>
+        <v>59.67599999999999</v>
       </c>
       <c r="F88">
-        <v>98.72799999999999</v>
+        <v>99.87599999999999</v>
       </c>
       <c r="G88">
         <v>5.9</v>
@@ -8497,28 +8497,28 @@
         <v>19.5</v>
       </c>
       <c r="M88">
-        <v>6.3284648</v>
+        <v>6.4020516</v>
       </c>
       <c r="N88">
-        <v>13.1715352</v>
+        <v>13.0979484</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>13.1715352</v>
+        <v>13.0979484</v>
       </c>
       <c r="Q88">
-        <v>15.7715352</v>
+        <v>15.6979484</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3079928321045248</v>
+        <v>0.3281615114971805</v>
       </c>
       <c r="T88">
-        <v>5.110626316978949</v>
+        <v>5.503751418285022</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.081316024701599</v>
+        <v>3.045898599130316</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09842799649463348</v>
+        <v>0.09861099649463348</v>
       </c>
       <c r="C89">
-        <v>6.368990285897809</v>
+        <v>5.071568980444056</v>
       </c>
       <c r="D89">
-        <v>100.3449902858978</v>
+        <v>100.1955689804441</v>
       </c>
       <c r="E89">
-        <v>59.67599999999999</v>
+        <v>60.824</v>
       </c>
       <c r="F89">
-        <v>99.87599999999999</v>
+        <v>101.024</v>
       </c>
       <c r="G89">
         <v>5.9</v>
@@ -8579,28 +8579,28 @@
         <v>19.5</v>
       </c>
       <c r="M89">
-        <v>6.4020516</v>
+        <v>6.4756384</v>
       </c>
       <c r="N89">
-        <v>13.0979484</v>
+        <v>13.0243616</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>13.0979484</v>
+        <v>13.0243616</v>
       </c>
       <c r="Q89">
-        <v>15.6979484</v>
+        <v>15.6243616</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3281615114971805</v>
+        <v>0.3516916374552789</v>
       </c>
       <c r="T89">
-        <v>5.503751418285022</v>
+        <v>5.962397369808775</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.045898599130316</v>
+        <v>3.01128611504929</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09861099649463348</v>
+        <v>0.1057359964946335</v>
       </c>
       <c r="C90">
-        <v>5.071568980444056</v>
+        <v>-1.56707368674364</v>
       </c>
       <c r="D90">
-        <v>100.1955689804441</v>
+        <v>94.70492631325635</v>
       </c>
       <c r="E90">
-        <v>60.824</v>
+        <v>61.97199999999999</v>
       </c>
       <c r="F90">
-        <v>101.024</v>
+        <v>102.172</v>
       </c>
       <c r="G90">
         <v>5.9</v>
@@ -8661,45 +8661,45 @@
         <v>19.5</v>
       </c>
       <c r="M90">
-        <v>6.4756384</v>
+        <v>7.346166800000001</v>
       </c>
       <c r="N90">
-        <v>13.0243616</v>
+        <v>12.1538332</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>13.0243616</v>
+        <v>12.1538332</v>
       </c>
       <c r="Q90">
-        <v>15.6243616</v>
+        <v>14.7538332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3516916374552789</v>
+        <v>0.3794999681330316</v>
       </c>
       <c r="T90">
-        <v>5.962397369808775</v>
+        <v>6.504433494336845</v>
       </c>
       <c r="U90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.01128611504929</v>
+        <v>2.654445581061404</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1057359964946335</v>
+        <v>0.1059969964946335</v>
       </c>
       <c r="C91">
-        <v>-1.56707368674364</v>
+        <v>-2.904801915493238</v>
       </c>
       <c r="D91">
-        <v>94.70492631325635</v>
+        <v>94.51519808450675</v>
       </c>
       <c r="E91">
-        <v>61.97199999999999</v>
+        <v>63.11999999999999</v>
       </c>
       <c r="F91">
-        <v>102.172</v>
+        <v>103.32</v>
       </c>
       <c r="G91">
         <v>5.9</v>
@@ -8743,28 +8743,28 @@
         <v>19.5</v>
       </c>
       <c r="M91">
-        <v>7.346166800000001</v>
+        <v>7.428708</v>
       </c>
       <c r="N91">
-        <v>12.1538332</v>
+        <v>12.071292</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>12.1538332</v>
+        <v>12.071292</v>
       </c>
       <c r="Q91">
-        <v>14.7538332</v>
+        <v>14.671292</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3794999681330316</v>
+        <v>0.4128699649463348</v>
       </c>
       <c r="T91">
-        <v>6.504433494336845</v>
+        <v>7.154876843770531</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.654445581061404</v>
+        <v>2.624951741271834</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1059969964946335</v>
+        <v>0.1062579964946335</v>
       </c>
       <c r="C92">
-        <v>-2.904801915493238</v>
+        <v>-4.241771475570545</v>
       </c>
       <c r="D92">
-        <v>94.51519808450675</v>
+        <v>94.32622852442945</v>
       </c>
       <c r="E92">
-        <v>63.11999999999999</v>
+        <v>64.268</v>
       </c>
       <c r="F92">
-        <v>103.32</v>
+        <v>104.468</v>
       </c>
       <c r="G92">
         <v>5.9</v>
@@ -8825,28 +8825,28 @@
         <v>19.5</v>
       </c>
       <c r="M92">
-        <v>7.428708</v>
+        <v>7.511249200000001</v>
       </c>
       <c r="N92">
-        <v>12.071292</v>
+        <v>11.9887508</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>12.071292</v>
+        <v>11.9887508</v>
       </c>
       <c r="Q92">
-        <v>14.671292</v>
+        <v>14.5887508</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4128699649463348</v>
+        <v>0.4536555166070387</v>
       </c>
       <c r="T92">
-        <v>7.154876843770531</v>
+        <v>7.949863159745035</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.624951741271834</v>
+        <v>2.596106117741373</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1062579964946335</v>
+        <v>0.1065189964946335</v>
       </c>
       <c r="C93">
-        <v>-4.241771475570545</v>
+        <v>-5.577986908442611</v>
       </c>
       <c r="D93">
-        <v>94.32622852442945</v>
+        <v>94.13801309155738</v>
       </c>
       <c r="E93">
-        <v>64.268</v>
+        <v>65.416</v>
       </c>
       <c r="F93">
-        <v>104.468</v>
+        <v>105.616</v>
       </c>
       <c r="G93">
         <v>5.9</v>
@@ -8907,28 +8907,28 @@
         <v>19.5</v>
       </c>
       <c r="M93">
-        <v>7.511249200000001</v>
+        <v>7.5937904</v>
       </c>
       <c r="N93">
-        <v>11.9887508</v>
+        <v>11.9062096</v>
       </c>
       <c r="O93">
         <v>0</v>
       </c>
       <c r="P93">
-        <v>11.9887508</v>
+        <v>11.9062096</v>
       </c>
       <c r="Q93">
-        <v>14.5887508</v>
+        <v>14.5062096</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4536555166070387</v>
+        <v>0.5046374561829187</v>
       </c>
       <c r="T93">
-        <v>7.949863159745035</v>
+        <v>8.943596054713167</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.596106117741373</v>
+        <v>2.567887572983315</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1065189964946335</v>
+        <v>0.1067799964946335</v>
       </c>
       <c r="C94">
-        <v>-5.577986908442611</v>
+        <v>-6.91345271940105</v>
       </c>
       <c r="D94">
-        <v>94.13801309155738</v>
+        <v>93.95054728059895</v>
       </c>
       <c r="E94">
-        <v>65.416</v>
+        <v>66.56400000000001</v>
       </c>
       <c r="F94">
-        <v>105.616</v>
+        <v>106.764</v>
       </c>
       <c r="G94">
         <v>5.9</v>
@@ -8989,28 +8989,28 @@
         <v>19.5</v>
       </c>
       <c r="M94">
-        <v>7.5937904</v>
+        <v>7.676331600000001</v>
       </c>
       <c r="N94">
-        <v>11.9062096</v>
+        <v>11.8236684</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>11.9062096</v>
+        <v>11.8236684</v>
       </c>
       <c r="Q94">
-        <v>14.5062096</v>
+        <v>14.4236684</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5046374561829187</v>
+        <v>0.5701856642090498</v>
       </c>
       <c r="T94">
-        <v>8.943596054713167</v>
+        <v>10.2212526339579</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.567887572983315</v>
+        <v>2.540275878650161</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1067799964946335</v>
+        <v>0.1070409964946335</v>
       </c>
       <c r="C95">
-        <v>-6.91345271940105</v>
+        <v>-8.24817337792166</v>
       </c>
       <c r="D95">
-        <v>93.95054728059895</v>
+        <v>93.76382662207834</v>
       </c>
       <c r="E95">
-        <v>66.56400000000001</v>
+        <v>67.712</v>
       </c>
       <c r="F95">
-        <v>106.764</v>
+        <v>107.912</v>
       </c>
       <c r="G95">
         <v>5.9</v>
@@ -9071,28 +9071,28 @@
         <v>19.5</v>
       </c>
       <c r="M95">
-        <v>7.676331600000001</v>
+        <v>7.758872800000001</v>
       </c>
       <c r="N95">
-        <v>11.8236684</v>
+        <v>11.7411272</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>11.8236684</v>
+        <v>11.7411272</v>
       </c>
       <c r="Q95">
-        <v>14.4236684</v>
+        <v>14.3411272</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5701856642090498</v>
+        <v>0.6575832749105583</v>
       </c>
       <c r="T95">
-        <v>10.2212526339579</v>
+        <v>11.92479473961756</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.540275878650161</v>
+        <v>2.513251667175159</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1070409964946335</v>
+        <v>0.1110069964946335</v>
       </c>
       <c r="C96">
-        <v>-8.24817337792166</v>
+        <v>-12.1448211197682</v>
       </c>
       <c r="D96">
-        <v>93.76382662207834</v>
+        <v>91.0151788802318</v>
       </c>
       <c r="E96">
-        <v>67.712</v>
+        <v>68.86</v>
       </c>
       <c r="F96">
-        <v>107.912</v>
+        <v>109.06</v>
       </c>
       <c r="G96">
         <v>5.9</v>
@@ -9153,45 +9153,45 @@
         <v>19.5</v>
       </c>
       <c r="M96">
-        <v>7.758872800000001</v>
+        <v>8.266748000000002</v>
       </c>
       <c r="N96">
-        <v>11.7411272</v>
+        <v>11.233252</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>11.7411272</v>
+        <v>11.233252</v>
       </c>
       <c r="Q96">
-        <v>14.3411272</v>
+        <v>13.833252</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6575832749105583</v>
+        <v>0.7799399298926704</v>
       </c>
       <c r="T96">
-        <v>11.92479473961756</v>
+        <v>14.30975368754108</v>
       </c>
       <c r="U96">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.513251667175159</v>
+        <v>2.358847759723654</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1110069964946335</v>
+        <v>0.1113069964946335</v>
       </c>
       <c r="C97">
-        <v>-12.1448211197682</v>
+        <v>-13.49419548177481</v>
       </c>
       <c r="D97">
-        <v>91.0151788802318</v>
+        <v>90.8138045182252</v>
       </c>
       <c r="E97">
-        <v>68.86</v>
+        <v>70.00800000000001</v>
       </c>
       <c r="F97">
-        <v>109.06</v>
+        <v>110.208</v>
       </c>
       <c r="G97">
         <v>5.9</v>
@@ -9235,28 +9235,28 @@
         <v>19.5</v>
       </c>
       <c r="M97">
-        <v>8.266748000000002</v>
+        <v>8.353766400000001</v>
       </c>
       <c r="N97">
-        <v>11.233252</v>
+        <v>11.1462336</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>11.233252</v>
+        <v>11.1462336</v>
       </c>
       <c r="Q97">
-        <v>13.833252</v>
+        <v>13.7462336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7799399298926704</v>
+        <v>0.9634749123658384</v>
       </c>
       <c r="T97">
-        <v>14.30975368754108</v>
+        <v>17.88719210942635</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.358847759723654</v>
+        <v>2.334276428893199</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1113069964946335</v>
+        <v>0.1116069964946335</v>
       </c>
       <c r="C98">
-        <v>-13.49419548177478</v>
+        <v>-14.84268071495045</v>
       </c>
       <c r="D98">
-        <v>90.81380451822521</v>
+        <v>90.61331928504954</v>
       </c>
       <c r="E98">
-        <v>70.008</v>
+        <v>71.15599999999999</v>
       </c>
       <c r="F98">
-        <v>110.208</v>
+        <v>111.356</v>
       </c>
       <c r="G98">
         <v>5.9</v>
@@ -9317,28 +9317,28 @@
         <v>19.5</v>
       </c>
       <c r="M98">
-        <v>8.353766400000001</v>
+        <v>8.440784799999999</v>
       </c>
       <c r="N98">
-        <v>11.1462336</v>
+        <v>11.0592152</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>11.1462336</v>
+        <v>11.0592152</v>
       </c>
       <c r="Q98">
-        <v>13.7462336</v>
+        <v>13.6592152</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9634749123658359</v>
+        <v>1.269366549821115</v>
       </c>
       <c r="T98">
-        <v>17.88719210942631</v>
+        <v>23.84958947923508</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.334276428893199</v>
+        <v>2.310211723440692</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1116069964946335</v>
+        <v>0.1119069964946335</v>
       </c>
       <c r="C99">
-        <v>-14.84268071495045</v>
+        <v>-16.19028269498352</v>
       </c>
       <c r="D99">
-        <v>90.61331928504954</v>
+        <v>90.41371730501646</v>
       </c>
       <c r="E99">
-        <v>71.15599999999999</v>
+        <v>72.30399999999999</v>
       </c>
       <c r="F99">
-        <v>111.356</v>
+        <v>112.504</v>
       </c>
       <c r="G99">
         <v>5.9</v>
@@ -9399,28 +9399,28 @@
         <v>19.5</v>
       </c>
       <c r="M99">
-        <v>8.440784799999999</v>
+        <v>8.527803199999999</v>
       </c>
       <c r="N99">
-        <v>11.0592152</v>
+        <v>10.9721968</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>11.0592152</v>
+        <v>10.9721968</v>
       </c>
       <c r="Q99">
-        <v>13.6592152</v>
+        <v>13.5721968</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.269366549821115</v>
+        <v>1.881149824731672</v>
       </c>
       <c r="T99">
-        <v>23.84958947923508</v>
+        <v>35.77438421885262</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.310211723440692</v>
+        <v>2.286638134425992</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1119069964946335</v>
+        <v>0.1122069964946335</v>
       </c>
       <c r="C100">
-        <v>-16.19028269498352</v>
+        <v>-17.53700724590458</v>
       </c>
       <c r="D100">
-        <v>90.41371730501646</v>
+        <v>90.21499275409542</v>
       </c>
       <c r="E100">
-        <v>72.30399999999999</v>
+        <v>73.452</v>
       </c>
       <c r="F100">
-        <v>112.504</v>
+        <v>113.652</v>
       </c>
       <c r="G100">
         <v>5.9</v>
@@ -9481,28 +9481,28 @@
         <v>19.5</v>
       </c>
       <c r="M100">
-        <v>8.527803199999999</v>
+        <v>8.614821600000001</v>
       </c>
       <c r="N100">
-        <v>10.9721968</v>
+        <v>10.8851784</v>
       </c>
       <c r="O100">
         <v>0</v>
       </c>
       <c r="P100">
-        <v>10.9721968</v>
+        <v>10.8851784</v>
       </c>
       <c r="Q100">
-        <v>13.5721968</v>
+        <v>13.4851784</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.881149824731672</v>
+        <v>3.716499649463344</v>
       </c>
       <c r="T100">
-        <v>35.77438421885262</v>
+        <v>71.54876843770523</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.286638134425992</v>
+        <v>2.263540779532799</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1122069964946335</v>
-      </c>
-      <c r="C101">
-        <v>-17.53700724590458</v>
-      </c>
-      <c r="D101">
-        <v>90.21499275409542</v>
-      </c>
-      <c r="E101">
-        <v>73.452</v>
-      </c>
-      <c r="F101">
-        <v>113.652</v>
-      </c>
-      <c r="G101">
-        <v>5.9</v>
-      </c>
-      <c r="H101">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.1</v>
-      </c>
-      <c r="K101">
-        <v>2.600000000000001</v>
-      </c>
-      <c r="L101">
-        <v>19.5</v>
-      </c>
-      <c r="M101">
-        <v>8.614821600000001</v>
-      </c>
-      <c r="N101">
-        <v>10.8851784</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>10.8851784</v>
-      </c>
-      <c r="Q101">
-        <v>13.4851784</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.716499649463344</v>
-      </c>
-      <c r="T101">
-        <v>71.54876843770523</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.263540779532799</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
